--- a/data/Ferry/CL32-May.xlsx
+++ b/data/Ferry/CL32-May.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adane\dm_tracker\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D853FD29-4164-4D99-A8C7-19795F02E78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FA70E7-566E-4592-AD40-BE8764689A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -876,8 +876,8 @@
     <col min="6" max="6" width="30.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" customWidth="1"/>
+    <col min="10" max="10" width="31.5703125" customWidth="1"/>
     <col min="11" max="11" width="73.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/Ferry/CL32-May.xlsx
+++ b/data/Ferry/CL32-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FA70E7-566E-4592-AD40-BE8764689A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E22E75-5D75-4443-8AD3-52672D20D1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
@@ -521,16 +521,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -870,10 +869,10 @@
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="96.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="35.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="30.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26.5703125" customWidth="1"/>
@@ -888,16 +887,16 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -923,16 +922,16 @@
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <v>46111</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="2">
         <v>46135</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="2">
         <v>46111</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>46135</v>
       </c>
       <c r="G2">
@@ -941,8 +940,8 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="1">
-        <v>1</v>
+      <c r="J2" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -952,16 +951,16 @@
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <v>46111</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="2">
         <v>46135</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="2">
         <v>46111</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>46135</v>
       </c>
       <c r="G3">
@@ -970,8 +969,8 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3" s="1">
-        <v>1</v>
+      <c r="J3" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -981,16 +980,16 @@
       <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <v>46122</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="2">
         <v>46135</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="2">
         <v>46122</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>46135</v>
       </c>
       <c r="G4">
@@ -999,8 +998,8 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4" s="1">
-        <v>1</v>
+      <c r="J4" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1010,16 +1009,16 @@
       <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>46136</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>46142</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>46136</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>46142</v>
       </c>
       <c r="G5">
@@ -1028,8 +1027,8 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5" s="1">
-        <v>1</v>
+      <c r="J5" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1039,16 +1038,16 @@
       <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>46143</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>46178</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="2">
         <v>46143</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>46164</v>
       </c>
       <c r="G6">
@@ -1060,8 +1059,8 @@
       <c r="I6">
         <v>5</v>
       </c>
-      <c r="J6" s="2">
-        <v>0.66669999999999996</v>
+      <c r="J6" s="3">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1071,16 +1070,16 @@
       <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>46143</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <v>46178</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="2">
         <v>46143</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>46164</v>
       </c>
       <c r="G7">
@@ -1092,8 +1091,8 @@
       <c r="I7">
         <v>5</v>
       </c>
-      <c r="J7" s="2">
-        <v>0.66669999999999996</v>
+      <c r="J7" s="3">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1103,16 +1102,16 @@
       <c r="B8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <v>46174</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <v>46185</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="2">
         <v>46143</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>46157</v>
       </c>
       <c r="G8">
@@ -1124,7 +1123,7 @@
       <c r="I8">
         <v>10</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1135,16 +1134,16 @@
       <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <v>46111</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <v>46114</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="2">
         <v>46111</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="2">
         <v>46114</v>
       </c>
       <c r="G9">
@@ -1153,8 +1152,8 @@
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" s="1">
-        <v>1</v>
+      <c r="J9" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1164,16 +1163,16 @@
       <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <v>46111</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <v>46114</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="2">
         <v>46111</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>46114</v>
       </c>
       <c r="G10">
@@ -1182,8 +1181,8 @@
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="1">
-        <v>1</v>
+      <c r="J10" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1193,16 +1192,16 @@
       <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <v>46111</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="2">
         <v>46114</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="2">
         <v>46111</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>46114</v>
       </c>
       <c r="G11">
@@ -1211,8 +1210,8 @@
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" s="1">
-        <v>1</v>
+      <c r="J11" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1222,16 +1221,16 @@
       <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <v>46111</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="2">
         <v>46114</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="2">
         <v>46111</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>46114</v>
       </c>
       <c r="G12">
@@ -1240,8 +1239,8 @@
       <c r="I12">
         <v>0</v>
       </c>
-      <c r="J12" s="1">
-        <v>1</v>
+      <c r="J12" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1251,12 +1250,12 @@
       <c r="B13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2">
         <v>46174</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
         <v>46147</v>
       </c>
       <c r="G13">
@@ -1268,7 +1267,7 @@
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="3">
         <v>0</v>
       </c>
       <c r="K13" t="s">
@@ -1282,16 +1281,16 @@
       <c r="B14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <v>46174</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="2">
         <v>46178</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="2">
         <v>46148</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>46154</v>
       </c>
       <c r="G14">
@@ -1303,7 +1302,7 @@
       <c r="I14">
         <v>5</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1314,16 +1313,16 @@
       <c r="B15" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <v>46181</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>46185</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="2">
         <v>46155</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>46161</v>
       </c>
       <c r="G15">
@@ -1335,7 +1334,7 @@
       <c r="I15">
         <v>5</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1346,16 +1345,16 @@
       <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <v>46188</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="2">
         <v>46199</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="2">
         <v>46162</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>46176</v>
       </c>
       <c r="G16">
@@ -1367,7 +1366,7 @@
       <c r="I16">
         <v>10</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1378,16 +1377,16 @@
       <c r="B17" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="2">
         <v>46202</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="2">
         <v>46206</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>46177</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>46183</v>
       </c>
       <c r="G17">
@@ -1399,7 +1398,7 @@
       <c r="I17">
         <v>5</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1410,16 +1409,16 @@
       <c r="B18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="2">
         <v>46111</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="2">
         <v>46114</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
         <v>46111</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>46114</v>
       </c>
       <c r="G18">
@@ -1428,8 +1427,8 @@
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="1">
-        <v>1</v>
+      <c r="J18" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1439,16 +1438,16 @@
       <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>46119</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>46125</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
         <v>46119</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>46125</v>
       </c>
       <c r="G19">
@@ -1457,8 +1456,8 @@
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="1">
-        <v>1</v>
+      <c r="J19" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1468,16 +1467,16 @@
       <c r="B20" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="2">
         <v>46126</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="2">
         <v>46132</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
         <v>46126</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>46132</v>
       </c>
       <c r="G20">
@@ -1486,8 +1485,8 @@
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20" s="1">
-        <v>1</v>
+      <c r="J20" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1497,16 +1496,16 @@
       <c r="B21" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="2">
         <v>46133</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="2">
         <v>46164</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>46133</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>46150</v>
       </c>
       <c r="G21">
@@ -1515,8 +1514,8 @@
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" s="1">
-        <v>1</v>
+      <c r="J21" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1526,16 +1525,16 @@
       <c r="B22" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>46168</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>46174</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="2">
         <v>46153</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>46157</v>
       </c>
       <c r="G22">
@@ -1547,8 +1546,8 @@
       <c r="I22">
         <v>1</v>
       </c>
-      <c r="J22" s="1">
-        <v>0.8</v>
+      <c r="J22" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1558,16 +1557,16 @@
       <c r="B23" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <v>46188</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
         <v>46199</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="2">
         <v>46162</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>46176</v>
       </c>
       <c r="G23">
@@ -1579,7 +1578,7 @@
       <c r="I23">
         <v>10</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1590,16 +1589,16 @@
       <c r="B24" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="2">
         <v>46111</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>46122</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="2">
         <v>46111</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>46122</v>
       </c>
       <c r="G24">
@@ -1608,8 +1607,8 @@
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" s="1">
-        <v>1</v>
+      <c r="J24" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1619,16 +1618,16 @@
       <c r="B25" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="2">
         <v>46125</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="2">
         <v>46136</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="2">
         <v>46125</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>46136</v>
       </c>
       <c r="G25">
@@ -1637,8 +1636,8 @@
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25" s="1">
-        <v>1</v>
+      <c r="J25" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1648,16 +1647,16 @@
       <c r="B26" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="2">
         <v>46139</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="2">
         <v>46164</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="2">
         <v>46139</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>46153</v>
       </c>
       <c r="G26">
@@ -1666,8 +1665,8 @@
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="1">
-        <v>1</v>
+      <c r="J26" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1677,16 +1676,16 @@
       <c r="B27" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="2">
         <v>46104</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="2">
         <v>46129</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="2">
         <v>46104</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="2">
         <v>46129</v>
       </c>
       <c r="G27">
@@ -1695,8 +1694,8 @@
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="1">
-        <v>1</v>
+      <c r="J27" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1706,16 +1705,16 @@
       <c r="B28" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="2">
         <v>46111</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="2">
         <v>46129</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="2">
         <v>46111</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="2">
         <v>46129</v>
       </c>
       <c r="G28">
@@ -1724,8 +1723,8 @@
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="1">
-        <v>1</v>
+      <c r="J28" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1735,16 +1734,16 @@
       <c r="B29" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="2">
         <v>46132</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>46136</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="2">
         <v>46132</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>46136</v>
       </c>
       <c r="G29">
@@ -1753,8 +1752,8 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="1">
-        <v>1</v>
+      <c r="J29" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1764,16 +1763,16 @@
       <c r="B30" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="2">
         <v>46202</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="2">
         <v>46213</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="2">
         <v>46177</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>46190</v>
       </c>
       <c r="G30">
@@ -1785,7 +1784,7 @@
       <c r="I30">
         <v>10</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1796,16 +1795,16 @@
       <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="2">
         <v>46097</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="2">
         <v>46101</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="2">
         <v>46097</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="2">
         <v>46101</v>
       </c>
       <c r="G31">
@@ -1814,8 +1813,8 @@
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" s="1">
-        <v>1</v>
+      <c r="J31" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1825,16 +1824,16 @@
       <c r="B32" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="2">
         <v>46188</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="2">
         <v>46192</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="2">
         <v>46162</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>46169</v>
       </c>
       <c r="G32">
@@ -1846,7 +1845,7 @@
       <c r="I32">
         <v>5</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1857,16 +1856,16 @@
       <c r="B33" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="2">
         <v>46195</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="2">
         <v>46206</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="2">
         <v>46170</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="2">
         <v>46183</v>
       </c>
       <c r="G33">
@@ -1878,7 +1877,7 @@
       <c r="I33">
         <v>10</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1889,16 +1888,16 @@
       <c r="B34" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="2">
         <v>46216</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="2">
         <v>46227</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="2">
         <v>46191</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>46204</v>
       </c>
       <c r="G34">
@@ -1910,7 +1909,7 @@
       <c r="I34">
         <v>10</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1921,16 +1920,16 @@
       <c r="B35" t="s">
         <v>80</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="2">
         <v>46230</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="2">
         <v>46234</v>
       </c>
-      <c r="E35" s="4">
+      <c r="E35" s="2">
         <v>46205</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <v>46211</v>
       </c>
       <c r="G35">
@@ -1942,7 +1941,7 @@
       <c r="I35">
         <v>5</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1953,16 +1952,16 @@
       <c r="B36" t="s">
         <v>82</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="2">
         <v>46237</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="2">
         <v>46248</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="2">
         <v>46212</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>46225</v>
       </c>
       <c r="G36">
@@ -1974,7 +1973,7 @@
       <c r="I36">
         <v>10</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1985,16 +1984,16 @@
       <c r="B37" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="2">
         <v>46251</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="2">
         <v>46255</v>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="2">
         <v>46226</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="2">
         <v>46232</v>
       </c>
       <c r="G37">
@@ -2006,7 +2005,7 @@
       <c r="I37">
         <v>5</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2017,16 +2016,16 @@
       <c r="B38" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="2">
         <v>46216</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="2">
         <v>46224</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="2">
         <v>46191</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="2">
         <v>46199</v>
       </c>
       <c r="G38">
@@ -2038,7 +2037,7 @@
       <c r="I38">
         <v>7</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2049,16 +2048,16 @@
       <c r="B39" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="2">
         <v>46225</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="2">
         <v>46231</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="2">
         <v>46202</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="2">
         <v>46206</v>
       </c>
       <c r="G39">
@@ -2070,7 +2069,7 @@
       <c r="I39">
         <v>5</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2081,16 +2080,16 @@
       <c r="B40" t="s">
         <v>90</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="2">
         <v>46232</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="2">
         <v>46238</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="2">
         <v>46209</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>46213</v>
       </c>
       <c r="G40">
@@ -2102,7 +2101,7 @@
       <c r="I40">
         <v>5</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2113,16 +2112,16 @@
       <c r="B41" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="2">
         <v>46239</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="2">
         <v>46245</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="2">
         <v>46216</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="2">
         <v>46220</v>
       </c>
       <c r="G41">
@@ -2134,7 +2133,7 @@
       <c r="I41">
         <v>5</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2145,16 +2144,16 @@
       <c r="B42" t="s">
         <v>94</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="2">
         <v>46246</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="2">
         <v>46252</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="2">
         <v>46223</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="2">
         <v>46227</v>
       </c>
       <c r="G42">
@@ -2166,7 +2165,7 @@
       <c r="I42">
         <v>5</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2177,16 +2176,16 @@
       <c r="B43" t="s">
         <v>96</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="2">
         <v>46253</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="2">
         <v>46259</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="2">
         <v>46230</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="2">
         <v>46234</v>
       </c>
       <c r="G43">
@@ -2198,7 +2197,7 @@
       <c r="I43">
         <v>5</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2209,16 +2208,16 @@
       <c r="B44" t="s">
         <v>98</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="2">
         <v>46216</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="2">
         <v>46220</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="2">
         <v>46191</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="2">
         <v>46197</v>
       </c>
       <c r="G44">
@@ -2230,7 +2229,7 @@
       <c r="I44">
         <v>5</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2241,16 +2240,16 @@
       <c r="B45" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="2">
         <v>46258</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="2">
         <v>46260</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="2">
         <v>46233</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="2">
         <v>46237</v>
       </c>
       <c r="G45">
@@ -2262,7 +2261,7 @@
       <c r="I45">
         <v>3</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2273,16 +2272,16 @@
       <c r="B46" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="2">
         <v>46237</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="2">
         <v>46241</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="2">
         <v>46212</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="2">
         <v>46218</v>
       </c>
       <c r="G46">
@@ -2294,7 +2293,7 @@
       <c r="I46">
         <v>5</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2305,16 +2304,16 @@
       <c r="B47" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="2">
         <v>46174</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="2">
         <v>46174</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="2">
         <v>46154</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="2">
         <v>46154</v>
       </c>
       <c r="G47">
@@ -2326,7 +2325,7 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2337,16 +2336,16 @@
       <c r="B48" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="2">
         <v>46174</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="2">
         <v>46183</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="2">
         <v>46155</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="2">
         <v>46169</v>
       </c>
       <c r="G48">
@@ -2358,7 +2357,7 @@
       <c r="I48">
         <v>8</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2369,16 +2368,16 @@
       <c r="B49" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="2">
         <v>46216</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="2">
         <v>46227</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="2">
         <v>46191</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="2">
         <v>46204</v>
       </c>
       <c r="G49">
@@ -2390,7 +2389,7 @@
       <c r="I49">
         <v>10</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2401,16 +2400,16 @@
       <c r="B50" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="2">
         <v>46237</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="2">
         <v>46241</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="2">
         <v>46212</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="2">
         <v>46218</v>
       </c>
       <c r="G50">
@@ -2422,7 +2421,7 @@
       <c r="I50">
         <v>5</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2433,16 +2432,16 @@
       <c r="B51" t="s">
         <v>112</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="2">
         <v>46237</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="2">
         <v>46241</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="2">
         <v>46212</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="2">
         <v>46218</v>
       </c>
       <c r="G51">
@@ -2454,7 +2453,7 @@
       <c r="I51">
         <v>5</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2465,16 +2464,16 @@
       <c r="B52" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="2">
         <v>46216</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="2">
         <v>46218</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="2">
         <v>46191</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="2">
         <v>46195</v>
       </c>
       <c r="G52">
@@ -2486,7 +2485,7 @@
       <c r="I52">
         <v>3</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2497,16 +2496,16 @@
       <c r="B53" t="s">
         <v>116</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="2">
         <v>46219</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="2">
         <v>46223</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="2">
         <v>46196</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="2">
         <v>46198</v>
       </c>
       <c r="G53">
@@ -2518,7 +2517,7 @@
       <c r="I53">
         <v>3</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2529,16 +2528,16 @@
       <c r="B54" t="s">
         <v>118</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="2">
         <v>46224</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="2">
         <v>46226</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="2">
         <v>46199</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="2">
         <v>46203</v>
       </c>
       <c r="G54">
@@ -2550,7 +2549,7 @@
       <c r="I54">
         <v>3</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J54" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2561,16 +2560,16 @@
       <c r="B55" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="2">
         <v>46227</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="2">
         <v>46231</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="2">
         <v>46204</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="2">
         <v>46206</v>
       </c>
       <c r="G55">
@@ -2582,7 +2581,7 @@
       <c r="I55">
         <v>3</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2593,16 +2592,16 @@
       <c r="B56" t="s">
         <v>122</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="2">
         <v>46232</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="2">
         <v>46245</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="2">
         <v>46209</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="2">
         <v>46220</v>
       </c>
       <c r="G56">
@@ -2614,7 +2613,7 @@
       <c r="I56">
         <v>10</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J56" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2625,16 +2624,16 @@
       <c r="B57" t="s">
         <v>124</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="2">
         <v>46232</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="2">
         <v>46234</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="2">
         <v>46209</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="2">
         <v>46211</v>
       </c>
       <c r="G57">
@@ -2646,7 +2645,7 @@
       <c r="I57">
         <v>3</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2657,16 +2656,16 @@
       <c r="B58" t="s">
         <v>126</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="2">
         <v>46160</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="2">
         <v>46168</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E58" s="2">
         <v>46139</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="2">
         <v>46153</v>
       </c>
       <c r="G58">
@@ -2675,8 +2674,8 @@
       <c r="I58">
         <v>0</v>
       </c>
-      <c r="J58" s="1">
-        <v>1</v>
+      <c r="J58" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -2686,16 +2685,16 @@
       <c r="B59" t="s">
         <v>128</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="2">
         <v>46168</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="2">
         <v>46170</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E59" s="2">
         <v>46154</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="2">
         <v>46156</v>
       </c>
       <c r="G59">
@@ -2704,8 +2703,8 @@
       <c r="I59">
         <v>0</v>
       </c>
-      <c r="J59" s="1">
-        <v>1</v>
+      <c r="J59" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -2715,16 +2714,16 @@
       <c r="B60" t="s">
         <v>130</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="2">
         <v>46169</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="2">
         <v>46175</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="2">
         <v>46154</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="2">
         <v>46160</v>
       </c>
       <c r="G60">
@@ -2736,8 +2735,8 @@
       <c r="I60">
         <v>2</v>
       </c>
-      <c r="J60" s="1">
-        <v>0.6</v>
+      <c r="J60" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -2747,16 +2746,16 @@
       <c r="B61" t="s">
         <v>132</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="2">
         <v>46171</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="2">
         <v>46184</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="2">
         <v>46157</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="2">
         <v>46171</v>
       </c>
       <c r="G61">
@@ -2768,8 +2767,8 @@
       <c r="I61">
         <v>9</v>
       </c>
-      <c r="J61" s="1">
-        <v>0.1</v>
+      <c r="J61" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -2779,16 +2778,16 @@
       <c r="B62" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="2">
         <v>46176</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="2">
         <v>46178</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="2">
         <v>46161</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="2">
         <v>46163</v>
       </c>
       <c r="G62">
@@ -2800,7 +2799,7 @@
       <c r="I62">
         <v>3</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2811,16 +2810,16 @@
       <c r="B63" t="s">
         <v>136</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="2">
         <v>46185</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="2">
         <v>46198</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="2">
         <v>46174</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="2">
         <v>46185</v>
       </c>
       <c r="G63">
@@ -2832,7 +2831,7 @@
       <c r="I63">
         <v>10</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J63" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2843,16 +2842,16 @@
       <c r="B64" t="s">
         <v>138</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="2">
         <v>46199</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="2">
         <v>46205</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E64" s="2">
         <v>46188</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="2">
         <v>46192</v>
       </c>
       <c r="G64">
@@ -2864,7 +2863,7 @@
       <c r="I64">
         <v>5</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2875,16 +2874,16 @@
       <c r="B65" t="s">
         <v>140</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="2">
         <v>46171</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="2">
         <v>46177</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="2">
         <v>46157</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="2">
         <v>46163</v>
       </c>
       <c r="G65">
@@ -2896,8 +2895,8 @@
       <c r="I65">
         <v>4</v>
       </c>
-      <c r="J65" s="1">
-        <v>0.2</v>
+      <c r="J65" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -2907,16 +2906,16 @@
       <c r="B66" t="s">
         <v>142</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="2">
         <v>46181</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="2">
         <v>46185</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="2">
         <v>46164</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="2">
         <v>46171</v>
       </c>
       <c r="G66">
@@ -2928,7 +2927,7 @@
       <c r="I66">
         <v>5</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2939,14 +2938,14 @@
       <c r="B67" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="2">
         <v>46261</v>
       </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4">
+      <c r="D67" s="2"/>
+      <c r="E67" s="2">
         <v>46238</v>
       </c>
-      <c r="F67" s="4"/>
+      <c r="F67" s="2"/>
       <c r="G67">
         <v>-17</v>
       </c>
@@ -2956,7 +2955,7 @@
       <c r="I67">
         <v>0</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J67" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2967,16 +2966,16 @@
       <c r="B68" t="s">
         <v>70</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="2">
         <v>46261</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="2">
         <v>46275</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="2">
         <v>46238</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="2">
         <v>46251</v>
       </c>
       <c r="G68">
@@ -2988,7 +2987,7 @@
       <c r="I68">
         <v>10</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="3">
         <v>0</v>
       </c>
     </row>
@@ -2999,16 +2998,16 @@
       <c r="B69" t="s">
         <v>146</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="2">
         <v>46276</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="2">
         <v>46289</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E69" s="2">
         <v>46252</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="2">
         <v>46266</v>
       </c>
       <c r="G69">
@@ -3020,7 +3019,7 @@
       <c r="I69">
         <v>10</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="3">
         <v>0</v>
       </c>
     </row>
@@ -3031,12 +3030,12 @@
       <c r="B70" t="s">
         <v>148</v>
       </c>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4">
+      <c r="C70" s="2"/>
+      <c r="D70" s="2">
         <v>46289</v>
       </c>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4">
+      <c r="E70" s="2"/>
+      <c r="F70" s="2">
         <v>46266</v>
       </c>
       <c r="G70">
@@ -3048,7 +3047,7 @@
       <c r="I70">
         <v>0</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70" s="3">
         <v>0</v>
       </c>
     </row>

--- a/data/Ferry/CL32-May.xlsx
+++ b/data/Ferry/CL32-May.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E22E75-5D75-4443-8AD3-52672D20D1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/Ferry/CL32-May.xlsx
+++ b/data/Ferry/CL32-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{2EBEC625-AEDC-41CF-9D3F-5442357843D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B92C531-2659-48CB-85B5-04EC6E35807E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E45988-8AFA-4155-B187-384D6986D8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="263">
   <si>
     <t>Activity ID</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Ferry PS Updated Scope May 26 CL32 Programme</t>
   </si>
   <si>
-    <t>16-Feb-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Key Dates</t>
   </si>
   <si>
@@ -131,12 +128,6 @@
     <t xml:space="preserve">  PMI's/EWN's/CE's</t>
   </si>
   <si>
-    <t>10-Apr-26 A</t>
-  </si>
-  <si>
-    <t>11-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-CHA-1010</t>
   </si>
   <si>
@@ -182,18 +173,12 @@
     <t>[GET] - Confirmation whether shaft lining is required</t>
   </si>
   <si>
-    <t>12-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-DEP-1040</t>
   </si>
   <si>
     <t>[GET] - Maximum flowrate in overflow pipe</t>
   </si>
   <si>
-    <t>13-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-DEP-1050</t>
   </si>
   <si>
@@ -206,9 +191,6 @@
     <t>[GET] - Manhole records/cards</t>
   </si>
   <si>
-    <t>20-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-DEP-1080</t>
   </si>
   <si>
@@ -245,45 +227,27 @@
     <t>[GET] - Catchment Area EPD (Explosion Protection Document)- Confirmation of Hazardous Substances in existing tank</t>
   </si>
   <si>
-    <t>01-Jun-26*</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Mobilisation</t>
   </si>
   <si>
-    <t>27-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1000</t>
   </si>
   <si>
     <t>Mobilisation</t>
   </si>
   <si>
-    <t>20-Feb-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1010</t>
   </si>
   <si>
     <t>Review Information and raise RFI/TQs</t>
   </si>
   <si>
-    <t>23-Feb-26 A</t>
-  </si>
-  <si>
-    <t>27-Feb-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1020</t>
   </si>
   <si>
     <t>Meeting with Murphy &amp; UU - Confirmation of revised scope received</t>
   </si>
   <si>
-    <t>09-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1030</t>
   </si>
   <si>
@@ -305,12 +269,6 @@
     <t xml:space="preserve">    JMS001-PS-RFQ-000001 - Optioneering Assessment</t>
   </si>
   <si>
-    <t>29-Apr-26 A</t>
-  </si>
-  <si>
-    <t>13-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CHA-1030</t>
   </si>
   <si>
@@ -347,9 +305,6 @@
     <t>Civil Modelling - Tank</t>
   </si>
   <si>
-    <t>24-Apr-26 A</t>
-  </si>
-  <si>
     <t>30-Apr-26 A</t>
   </si>
   <si>
@@ -359,9 +314,6 @@
     <t>Civil Modelling - Other Assets</t>
   </si>
   <si>
-    <t>01-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1070</t>
   </si>
   <si>
@@ -374,9 +326,6 @@
     <t>Network modelling (to be done by Arup)</t>
   </si>
   <si>
-    <t>21-May-26 A</t>
-  </si>
-  <si>
     <t>5 Day lag added from when optioneering is complete to allow ARUP to complete modelling</t>
   </si>
   <si>
@@ -395,9 +344,6 @@
     <t>Determine entry/exit levels for pipework to and from overflow pipe</t>
   </si>
   <si>
-    <t>02-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CSD-1010</t>
   </si>
   <si>
@@ -497,9 +443,6 @@
     <t>21-Apr-26 A</t>
   </si>
   <si>
-    <t>22-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1040</t>
   </si>
   <si>
@@ -551,9 +494,6 @@
     <t>[GET] response to JMS-MAE-TQ-000044</t>
   </si>
   <si>
-    <t>12-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      Process Design</t>
   </si>
   <si>
@@ -563,9 +503,6 @@
     <t>Basis of Design</t>
   </si>
   <si>
-    <t>17-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-PRO-1000</t>
   </si>
   <si>
@@ -713,9 +650,6 @@
     <t>Routing &amp; Design</t>
   </si>
   <si>
-    <t>27-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-PRO-1030</t>
   </si>
   <si>
@@ -728,9 +662,6 @@
     <t>HAZOP &amp; ALM action and close out</t>
   </si>
   <si>
-    <t>28-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        Documents</t>
   </si>
   <si>
@@ -794,9 +725,6 @@
     <t xml:space="preserve">      EICA Design</t>
   </si>
   <si>
-    <t>14-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-EICA-1100</t>
   </si>
   <si>
@@ -809,9 +737,6 @@
     <t>User Requirement Specification</t>
   </si>
   <si>
-    <t>18-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-EICA-1020</t>
   </si>
   <si>
@@ -830,9 +755,6 @@
     <t>Power Supply Assessment</t>
   </si>
   <si>
-    <t>29-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-EICA-1030</t>
   </si>
   <si>
@@ -903,9 +825,6 @@
   </si>
   <si>
     <t>[GET] - Historical asbuilt drawings</t>
-  </si>
-  <si>
-    <t>07-Oct-26*</t>
   </si>
 </sst>
 </file>
@@ -1285,8 +1204,10 @@
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="96.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" customWidth="1"/>
     <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -1333,8 +1254,8 @@
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
+      <c r="C2" s="1">
+        <v>46069</v>
       </c>
       <c r="D2" s="1">
         <v>46302</v>
@@ -1357,10 +1278,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
         <v>12</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46069</v>
       </c>
       <c r="D3" s="1">
         <v>46302</v>
@@ -1383,10 +1304,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46069</v>
       </c>
       <c r="D4" s="1">
         <v>46302</v>
@@ -1409,13 +1330,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
+      <c r="C5" s="1">
+        <v>46069</v>
       </c>
       <c r="E5" s="1">
         <v>46069</v>
@@ -1432,10 +1353,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>46290</v>
@@ -1464,14 +1385,14 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
-        <v>289</v>
+      <c r="D7" s="1">
+        <v>46302</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
@@ -1492,7 +1413,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
         <v>46185</v>
@@ -1518,10 +1439,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
       </c>
       <c r="D9" s="1">
         <v>46185</v>
@@ -1544,10 +1465,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>46202</v>
@@ -1570,10 +1491,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
         <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
       </c>
       <c r="D11" s="1">
         <v>46289</v>
@@ -1596,10 +1517,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
       </c>
       <c r="D12" s="1">
         <v>46289</v>
@@ -1622,13 +1543,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D13" s="1">
+        <v>46153</v>
       </c>
       <c r="E13" s="1">
         <v>46122</v>
@@ -1645,13 +1566,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
         <v>31</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46122</v>
       </c>
       <c r="E14" s="1">
         <v>46122</v>
@@ -1668,18 +1589,18 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>46135</v>
@@ -1696,13 +1617,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46153</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1713,10 +1634,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46069</v>
       </c>
       <c r="D18" s="1">
         <v>46174</v>
@@ -1739,13 +1660,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
+        <v>40</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46069</v>
       </c>
       <c r="E19" s="1">
         <v>46069</v>
@@ -1762,13 +1683,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
+        <v>42</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46069</v>
       </c>
       <c r="E20" s="1">
         <v>46069</v>
@@ -1785,13 +1706,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>48</v>
+        <v>44</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46093</v>
       </c>
       <c r="E21" s="1">
         <v>46093</v>
@@ -1808,13 +1729,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46094</v>
       </c>
       <c r="E22" s="1">
         <v>46094</v>
@@ -1831,13 +1752,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46094</v>
       </c>
       <c r="E23" s="1">
         <v>46094</v>
@@ -1854,13 +1775,13 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46101</v>
       </c>
       <c r="E24" s="1">
         <v>46101</v>
@@ -1877,13 +1798,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46101</v>
       </c>
       <c r="E25" s="1">
         <v>46101</v>
@@ -1900,13 +1821,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46101</v>
       </c>
       <c r="E26" s="1">
         <v>46101</v>
@@ -1923,13 +1844,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" t="s">
         <v>56</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46101</v>
       </c>
       <c r="E27" s="1">
         <v>46101</v>
@@ -1946,13 +1867,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46101</v>
       </c>
       <c r="E28" s="1">
         <v>46101</v>
@@ -1969,13 +1890,13 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46101</v>
       </c>
       <c r="E29" s="1">
         <v>46101</v>
@@ -1992,13 +1913,13 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" t="s">
-        <v>69</v>
+        <v>62</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46174</v>
       </c>
       <c r="E30" s="1">
         <v>46143</v>
@@ -2018,13 +1939,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>71</v>
+        <v>63</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46069</v>
+      </c>
+      <c r="D31" s="1">
+        <v>46108</v>
       </c>
       <c r="E31" s="1">
         <v>46069</v>
@@ -2041,16 +1962,16 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" t="s">
-        <v>74</v>
+        <v>65</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46069</v>
+      </c>
+      <c r="D32" s="1">
+        <v>46073</v>
       </c>
       <c r="E32" s="1">
         <v>46069</v>
@@ -2070,16 +1991,16 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" t="s">
-        <v>78</v>
+        <v>67</v>
+      </c>
+      <c r="C33" s="1">
+        <v>46076</v>
+      </c>
+      <c r="D33" s="1">
+        <v>46080</v>
       </c>
       <c r="E33" s="1">
         <v>46076</v>
@@ -2099,16 +2020,16 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" t="s">
-        <v>81</v>
+        <v>69</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46090</v>
+      </c>
+      <c r="D34" s="1">
+        <v>46090</v>
       </c>
       <c r="E34" s="1">
         <v>46090</v>
@@ -2128,16 +2049,16 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" t="s">
-        <v>51</v>
+        <v>71</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46090</v>
+      </c>
+      <c r="D35" s="1">
+        <v>46094</v>
       </c>
       <c r="E35" s="1">
         <v>46090</v>
@@ -2157,16 +2078,16 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46097</v>
+      </c>
+      <c r="D36" s="1">
+        <v>46108</v>
       </c>
       <c r="E36" s="1">
         <v>46097</v>
@@ -2186,10 +2107,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" t="s">
-        <v>86</v>
+        <v>75</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46097</v>
       </c>
       <c r="D37" s="1">
         <v>46289</v>
@@ -2212,13 +2133,13 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" t="s">
-        <v>90</v>
+        <v>76</v>
+      </c>
+      <c r="C38" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D38" s="1">
+        <v>46155</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2226,16 +2147,16 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" t="s">
-        <v>90</v>
+        <v>78</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46141</v>
+      </c>
+      <c r="D39" s="1">
+        <v>46155</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2246,10 +2167,10 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>94</v>
+        <v>79</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46111</v>
       </c>
       <c r="D40" s="1">
         <v>46185</v>
@@ -2272,16 +2193,16 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" t="s">
-        <v>94</v>
-      </c>
-      <c r="D41" t="s">
-        <v>38</v>
+        <v>82</v>
+      </c>
+      <c r="C41" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D41" s="1">
+        <v>46135</v>
       </c>
       <c r="E41" s="1">
         <v>46111</v>
@@ -2301,16 +2222,16 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" t="s">
-        <v>94</v>
-      </c>
-      <c r="D42" t="s">
-        <v>38</v>
+        <v>84</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D42" s="1">
+        <v>46135</v>
       </c>
       <c r="E42" s="1">
         <v>46111</v>
@@ -2330,16 +2251,16 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" t="s">
-        <v>31</v>
-      </c>
-      <c r="D43" t="s">
-        <v>38</v>
+        <v>86</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D43" s="1">
+        <v>46135</v>
       </c>
       <c r="E43" s="1">
         <v>46122</v>
@@ -2359,16 +2280,16 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
-      </c>
-      <c r="C44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" t="s">
-        <v>104</v>
+        <v>88</v>
+      </c>
+      <c r="C44" s="1">
+        <v>46136</v>
+      </c>
+      <c r="D44" s="1">
+        <v>46142</v>
       </c>
       <c r="E44" s="1">
         <v>46136</v>
@@ -2388,13 +2309,13 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
-      </c>
-      <c r="C45" t="s">
-        <v>107</v>
+        <v>91</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46143</v>
       </c>
       <c r="D45" s="1">
         <v>46178</v>
@@ -2420,13 +2341,13 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" t="s">
-        <v>107</v>
+        <v>93</v>
+      </c>
+      <c r="C46" s="1">
+        <v>46143</v>
       </c>
       <c r="D46" s="1">
         <v>46178</v>
@@ -2452,13 +2373,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" t="s">
-        <v>112</v>
+        <v>95</v>
+      </c>
+      <c r="C47" s="1">
+        <v>46163</v>
       </c>
       <c r="E47" s="1">
         <v>46143</v>
@@ -2473,15 +2394,15 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="C48" s="1">
         <v>46174</v>
@@ -2510,10 +2431,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>116</v>
-      </c>
-      <c r="C49" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46111</v>
       </c>
       <c r="D49" s="1">
         <v>46206</v>
@@ -2536,16 +2457,16 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B50" t="s">
-        <v>118</v>
-      </c>
-      <c r="C50" t="s">
-        <v>94</v>
-      </c>
-      <c r="D50" t="s">
-        <v>119</v>
+        <v>101</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D50" s="1">
+        <v>46114</v>
       </c>
       <c r="E50" s="1">
         <v>46111</v>
@@ -2565,16 +2486,16 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
-      </c>
-      <c r="C51" t="s">
-        <v>94</v>
-      </c>
-      <c r="D51" t="s">
-        <v>119</v>
+        <v>103</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D51" s="1">
+        <v>46114</v>
       </c>
       <c r="E51" s="1">
         <v>46111</v>
@@ -2594,16 +2515,16 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>123</v>
-      </c>
-      <c r="C52" t="s">
-        <v>94</v>
-      </c>
-      <c r="D52" t="s">
-        <v>119</v>
+        <v>105</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D52" s="1">
+        <v>46114</v>
       </c>
       <c r="E52" s="1">
         <v>46111</v>
@@ -2623,16 +2544,16 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" t="s">
-        <v>94</v>
-      </c>
-      <c r="D53" t="s">
-        <v>119</v>
+        <v>107</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D53" s="1">
+        <v>46114</v>
       </c>
       <c r="E53" s="1">
         <v>46111</v>
@@ -2652,13 +2573,13 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
-      </c>
-      <c r="D54" t="s">
-        <v>69</v>
+        <v>109</v>
+      </c>
+      <c r="D54" s="1">
+        <v>46174</v>
       </c>
       <c r="F54" s="1">
         <v>46147</v>
@@ -2676,15 +2597,15 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C55" s="1">
         <v>46174</v>
@@ -2713,10 +2634,10 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="C56" s="1">
         <v>46181</v>
@@ -2745,10 +2666,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="C57" s="1">
         <v>46188</v>
@@ -2777,10 +2698,10 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C58" s="1">
         <v>46202</v>
@@ -2809,10 +2730,10 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="D59" s="1">
         <v>46213</v>
@@ -2835,10 +2756,10 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D60" s="1">
         <v>46199</v>
@@ -2861,16 +2782,16 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
-      </c>
-      <c r="D61" t="s">
-        <v>119</v>
+        <v>80</v>
+      </c>
+      <c r="D61" s="1">
+        <v>46114</v>
       </c>
       <c r="E61" s="1">
         <v>46111</v>
@@ -2890,16 +2811,16 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
-      </c>
-      <c r="D62" t="s">
-        <v>145</v>
+        <v>126</v>
+      </c>
+      <c r="D62" s="1">
+        <v>46125</v>
       </c>
       <c r="E62" s="1">
         <v>46119</v>
@@ -2919,16 +2840,16 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C63" t="s">
-        <v>148</v>
-      </c>
-      <c r="D63" t="s">
-        <v>149</v>
+        <v>130</v>
+      </c>
+      <c r="D63" s="1">
+        <v>46132</v>
       </c>
       <c r="E63" s="1">
         <v>46126</v>
@@ -2948,16 +2869,16 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>152</v>
-      </c>
-      <c r="D64" t="s">
-        <v>153</v>
+        <v>134</v>
+      </c>
+      <c r="D64" s="1">
+        <v>46164</v>
       </c>
       <c r="E64" s="1">
         <v>46133</v>
@@ -2977,13 +2898,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D65" s="1">
         <v>46174</v>
@@ -3009,10 +2930,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C66" s="1">
         <v>46188</v>
@@ -3041,13 +2962,13 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
-      </c>
-      <c r="D67" t="s">
-        <v>153</v>
+        <v>80</v>
+      </c>
+      <c r="D67" s="1">
+        <v>46164</v>
       </c>
       <c r="E67" s="1">
         <v>46111</v>
@@ -3064,16 +2985,16 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
-      </c>
-      <c r="D68" t="s">
-        <v>31</v>
+        <v>80</v>
+      </c>
+      <c r="D68" s="1">
+        <v>46122</v>
       </c>
       <c r="E68" s="1">
         <v>46111</v>
@@ -3093,16 +3014,16 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="C69" t="s">
-        <v>145</v>
-      </c>
-      <c r="D69" t="s">
-        <v>103</v>
+        <v>127</v>
+      </c>
+      <c r="D69" s="1">
+        <v>46136</v>
       </c>
       <c r="E69" s="1">
         <v>46125</v>
@@ -3122,16 +3043,16 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C70" t="s">
-        <v>166</v>
-      </c>
-      <c r="D70" t="s">
-        <v>153</v>
+        <v>147</v>
+      </c>
+      <c r="D70" s="1">
+        <v>46164</v>
       </c>
       <c r="E70" s="1">
         <v>46139</v>
@@ -3151,13 +3072,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3168,13 +3089,13 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
-      </c>
-      <c r="D72" t="s">
-        <v>171</v>
+        <v>151</v>
+      </c>
+      <c r="D72" s="1">
+        <v>46154</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3185,13 +3106,13 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>138</v>
-      </c>
-      <c r="D73" t="s">
-        <v>103</v>
+        <v>120</v>
+      </c>
+      <c r="D73" s="1">
+        <v>46136</v>
       </c>
       <c r="E73" s="1">
         <v>46104</v>
@@ -3208,16 +3129,16 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="B74" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
-      </c>
-      <c r="D74" t="s">
-        <v>175</v>
+        <v>120</v>
+      </c>
+      <c r="D74" s="1">
+        <v>46129</v>
       </c>
       <c r="E74" s="1">
         <v>46104</v>
@@ -3237,16 +3158,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="B75" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
-      </c>
-      <c r="D75" t="s">
-        <v>175</v>
+        <v>80</v>
+      </c>
+      <c r="D75" s="1">
+        <v>46129</v>
       </c>
       <c r="E75" s="1">
         <v>46111</v>
@@ -3266,16 +3187,16 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="B76" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="C76" t="s">
-        <v>149</v>
-      </c>
-      <c r="D76" t="s">
-        <v>103</v>
+        <v>131</v>
+      </c>
+      <c r="D76" s="1">
+        <v>46136</v>
       </c>
       <c r="E76" s="1">
         <v>46132</v>
@@ -3295,7 +3216,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="C77" s="1">
         <v>46202</v>
@@ -3321,10 +3242,10 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="B78" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="C78" s="1">
         <v>46202</v>
@@ -3347,10 +3268,10 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="B79" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="C79" s="1">
         <v>46202</v>
@@ -3379,10 +3300,10 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D80" s="1">
         <v>46289</v>
@@ -3405,10 +3326,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D81" s="1">
         <v>46206</v>
@@ -3431,16 +3352,16 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="B82" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
-      </c>
-      <c r="D82" t="s">
-        <v>56</v>
+        <v>74</v>
+      </c>
+      <c r="D82" s="1">
+        <v>46101</v>
       </c>
       <c r="E82" s="1">
         <v>46097</v>
@@ -3460,10 +3381,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="B83" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="C83" s="1">
         <v>46188</v>
@@ -3492,10 +3413,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="B84" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="C84" s="1">
         <v>46195</v>
@@ -3524,7 +3445,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C85" s="1">
         <v>46216</v>
@@ -3550,7 +3471,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="C86" s="1">
         <v>46216</v>
@@ -3576,10 +3497,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="B87" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C87" s="1">
         <v>46216</v>
@@ -3608,10 +3529,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B88" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="C88" s="1">
         <v>46230</v>
@@ -3640,10 +3561,10 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="B89" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="C89" s="1">
         <v>46237</v>
@@ -3672,10 +3593,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="B90" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="C90" s="1">
         <v>46251</v>
@@ -3704,7 +3625,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C91" s="1">
         <v>46216</v>
@@ -3730,10 +3651,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="B92" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="C92" s="1">
         <v>46216</v>
@@ -3762,10 +3683,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C93" s="1">
         <v>46225</v>
@@ -3794,10 +3715,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="B94" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C94" s="1">
         <v>46232</v>
@@ -3826,7 +3747,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C95" s="1">
         <v>46239</v>
@@ -3852,10 +3773,10 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="B96" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="C96" s="1">
         <v>46239</v>
@@ -3884,10 +3805,10 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="B97" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C97" s="1">
         <v>46246</v>
@@ -3916,10 +3837,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="B98" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="C98" s="1">
         <v>46253</v>
@@ -3948,7 +3869,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C99" s="1">
         <v>46216</v>
@@ -3974,10 +3895,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="B100" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="C100" s="1">
         <v>46216</v>
@@ -4006,7 +3927,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C101" s="1">
         <v>46258</v>
@@ -4032,10 +3953,10 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="B102" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="C102" s="1">
         <v>46258</v>
@@ -4064,7 +3985,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="C103" s="1">
         <v>46237</v>
@@ -4090,10 +4011,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="B104" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C104" s="1">
         <v>46237</v>
@@ -4122,7 +4043,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="C105" s="1">
         <v>46174</v>
@@ -4148,10 +4069,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="B106" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C106" s="1">
         <v>46174</v>
@@ -4180,10 +4101,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="B107" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C107" s="1">
         <v>46174</v>
@@ -4212,7 +4133,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C108" s="1">
         <v>46216</v>
@@ -4238,7 +4159,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="C109" s="1">
         <v>46216</v>
@@ -4264,10 +4185,10 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="B110" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="C110" s="1">
         <v>46216</v>
@@ -4296,10 +4217,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="B111" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="C111" s="1">
         <v>46237</v>
@@ -4328,10 +4249,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="B112" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="C112" s="1">
         <v>46237</v>
@@ -4360,7 +4281,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="C113" s="1">
         <v>46216</v>
@@ -4386,10 +4307,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B114" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="C114" s="1">
         <v>46216</v>
@@ -4418,10 +4339,10 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B115" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="C115" s="1">
         <v>46219</v>
@@ -4450,10 +4371,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B116" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="C116" s="1">
         <v>46224</v>
@@ -4482,10 +4403,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="B117" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="C117" s="1">
         <v>46227</v>
@@ -4514,10 +4435,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="B118" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C118" s="1">
         <v>46232</v>
@@ -4546,10 +4467,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="B119" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="C119" s="1">
         <v>46232</v>
@@ -4578,10 +4499,10 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>251</v>
-      </c>
-      <c r="C120" t="s">
-        <v>252</v>
+        <v>228</v>
+      </c>
+      <c r="C120" s="1">
+        <v>46156</v>
       </c>
       <c r="D120" s="1">
         <v>46205</v>
@@ -4604,10 +4525,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>231</v>
-      </c>
-      <c r="C121" t="s">
-        <v>252</v>
+        <v>208</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46156</v>
       </c>
       <c r="D121" s="1">
         <v>46205</v>
@@ -4630,13 +4551,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="B122" t="s">
-        <v>254</v>
-      </c>
-      <c r="C122" t="s">
-        <v>252</v>
+        <v>230</v>
+      </c>
+      <c r="C122" s="1">
+        <v>46156</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -4647,16 +4568,16 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="B123" t="s">
-        <v>256</v>
-      </c>
-      <c r="C123" t="s">
-        <v>257</v>
-      </c>
-      <c r="D123" t="s">
-        <v>156</v>
+        <v>232</v>
+      </c>
+      <c r="C123" s="1">
+        <v>46160</v>
+      </c>
+      <c r="D123" s="1">
+        <v>46168</v>
       </c>
       <c r="E123" s="1">
         <v>46139</v>
@@ -4676,16 +4597,16 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="B124" t="s">
-        <v>259</v>
-      </c>
-      <c r="C124" t="s">
-        <v>156</v>
-      </c>
-      <c r="D124" t="s">
-        <v>230</v>
+        <v>234</v>
+      </c>
+      <c r="C124" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D124" s="1">
+        <v>46170</v>
       </c>
       <c r="E124" s="1">
         <v>46154</v>
@@ -4705,13 +4626,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
-      </c>
-      <c r="C125" t="s">
-        <v>225</v>
+        <v>236</v>
+      </c>
+      <c r="C125" s="1">
+        <v>46169</v>
       </c>
       <c r="D125" s="1">
         <v>46175</v>
@@ -4737,13 +4658,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="B126" t="s">
-        <v>263</v>
-      </c>
-      <c r="C126" t="s">
-        <v>264</v>
+        <v>238</v>
+      </c>
+      <c r="C126" s="1">
+        <v>46171</v>
       </c>
       <c r="D126" s="1">
         <v>46184</v>
@@ -4769,10 +4690,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="B127" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="C127" s="1">
         <v>46176</v>
@@ -4801,10 +4722,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="B128" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="C128" s="1">
         <v>46185</v>
@@ -4833,10 +4754,10 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="B129" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="C129" s="1">
         <v>46199</v>
@@ -4865,10 +4786,10 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>238</v>
-      </c>
-      <c r="C130" t="s">
-        <v>264</v>
+        <v>215</v>
+      </c>
+      <c r="C130" s="1">
+        <v>46171</v>
       </c>
       <c r="D130" s="1">
         <v>46192</v>
@@ -4891,13 +4812,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="B131" t="s">
-        <v>272</v>
-      </c>
-      <c r="C131" t="s">
-        <v>264</v>
+        <v>246</v>
+      </c>
+      <c r="C131" s="1">
+        <v>46171</v>
       </c>
       <c r="D131" s="1">
         <v>46177</v>
@@ -4923,10 +4844,10 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="B132" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="C132" s="1">
         <v>46181</v>
@@ -4955,10 +4876,10 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="B133" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="C133" s="1">
         <v>46188</v>
@@ -4987,7 +4908,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="C134" s="1">
         <v>46261</v>
@@ -5013,10 +4934,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="B135" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="C135" s="1">
         <v>46261</v>
@@ -5039,10 +4960,10 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="B136" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="C136" s="1">
         <v>46261</v>
@@ -5071,10 +4992,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
       <c r="B137" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="C137" s="1">
         <v>46276</v>
@@ -5103,10 +5024,10 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="B138" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D138" s="1">
         <v>46289</v>
@@ -5129,13 +5050,13 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>284</v>
-      </c>
-      <c r="C139" t="s">
-        <v>51</v>
-      </c>
-      <c r="D139" t="s">
-        <v>56</v>
+        <v>258</v>
+      </c>
+      <c r="C139" s="1">
+        <v>46094</v>
+      </c>
+      <c r="D139" s="1">
+        <v>46101</v>
       </c>
       <c r="E139" s="1">
         <v>46094</v>
@@ -5152,13 +5073,13 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="B140" t="s">
-        <v>286</v>
-      </c>
-      <c r="C140" t="s">
-        <v>51</v>
+        <v>260</v>
+      </c>
+      <c r="C140" s="1">
+        <v>46094</v>
       </c>
       <c r="E140" s="1">
         <v>46094</v>
@@ -5175,13 +5096,13 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="B141" t="s">
-        <v>288</v>
-      </c>
-      <c r="C141" t="s">
-        <v>56</v>
+        <v>262</v>
+      </c>
+      <c r="C141" s="1">
+        <v>46101</v>
       </c>
       <c r="E141" s="1">
         <v>46101</v>

--- a/data/Ferry/CL32-May.xlsx
+++ b/data/Ferry/CL32-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E45988-8AFA-4155-B187-384D6986D8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5AD563-D512-4745-B573-605061D93836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="252">
   <si>
     <t>Activity ID</t>
   </si>
@@ -260,9 +260,6 @@
     <t>Murphy Response to TQs</t>
   </si>
   <si>
-    <t>16-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Deliverables</t>
   </si>
   <si>
@@ -278,9 +275,6 @@
     <t xml:space="preserve">    3D Modelling</t>
   </si>
   <si>
-    <t>30-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1020</t>
   </si>
   <si>
@@ -305,9 +299,6 @@
     <t>Civil Modelling - Tank</t>
   </si>
   <si>
-    <t>30-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1060</t>
   </si>
   <si>
@@ -398,9 +389,6 @@
     <t xml:space="preserve">    Outline Design Scope Freeze (Minimum Requirements)</t>
   </si>
   <si>
-    <t>23-Mar-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">      Civils Design</t>
   </si>
   <si>
@@ -416,42 +404,24 @@
     <t>Outline drawing for connection into existing manhole on inlet pipe</t>
   </si>
   <si>
-    <t>07-Apr-26 A</t>
-  </si>
-  <si>
-    <t>13-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1020</t>
   </si>
   <si>
     <t>GA &amp; Long sections of pipe entry/exit pipework from new MHs</t>
   </si>
   <si>
-    <t>14-Apr-26 A</t>
-  </si>
-  <si>
-    <t>20-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1030</t>
   </si>
   <si>
     <t>Valve chamber standard detail drawing showing dimensions and layout</t>
   </si>
   <si>
-    <t>21-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1040</t>
   </si>
   <si>
     <t>Kiosk slab proposal</t>
   </si>
   <si>
-    <t>26-May-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1050</t>
   </si>
   <si>
@@ -477,9 +447,6 @@
   </si>
   <si>
     <t>Pump system curve and calcs with pump selection</t>
-  </si>
-  <si>
-    <t>27-Apr-26 A</t>
   </si>
   <si>
     <t xml:space="preserve">        FER-MEC-1120</t>
@@ -2107,7 +2074,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1">
         <v>46097</v>
@@ -2133,7 +2100,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C38" s="1">
         <v>46141</v>
@@ -2147,10 +2114,10 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
         <v>77</v>
-      </c>
-      <c r="B39" t="s">
-        <v>78</v>
       </c>
       <c r="C39" s="1">
         <v>46141</v>
@@ -2167,7 +2134,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C40" s="1">
         <v>46111</v>
@@ -2193,10 +2160,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C41" s="1">
         <v>46111</v>
@@ -2222,10 +2189,10 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C42" s="1">
         <v>46111</v>
@@ -2251,10 +2218,10 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C43" s="1">
         <v>46122</v>
@@ -2280,10 +2247,10 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C44" s="1">
         <v>46136</v>
@@ -2309,10 +2276,10 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C45" s="1">
         <v>46143</v>
@@ -2341,10 +2308,10 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C46" s="1">
         <v>46143</v>
@@ -2373,10 +2340,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C47" s="1">
         <v>46163</v>
@@ -2394,15 +2361,15 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C48" s="1">
         <v>46174</v>
@@ -2431,7 +2398,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C49" s="1">
         <v>46111</v>
@@ -2457,10 +2424,10 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C50" s="1">
         <v>46111</v>
@@ -2486,10 +2453,10 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C51" s="1">
         <v>46111</v>
@@ -2515,10 +2482,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C52" s="1">
         <v>46111</v>
@@ -2544,10 +2511,10 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C53" s="1">
         <v>46111</v>
@@ -2573,10 +2540,10 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D54" s="1">
         <v>46174</v>
@@ -2597,15 +2564,15 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C55" s="1">
         <v>46174</v>
@@ -2634,10 +2601,10 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B56" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C56" s="1">
         <v>46181</v>
@@ -2666,10 +2633,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C57" s="1">
         <v>46188</v>
@@ -2698,10 +2665,10 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C58" s="1">
         <v>46202</v>
@@ -2730,10 +2697,10 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>119</v>
-      </c>
-      <c r="C59" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="C59" s="1">
+        <v>46104</v>
       </c>
       <c r="D59" s="1">
         <v>46213</v>
@@ -2756,10 +2723,10 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" t="s">
-        <v>80</v>
+        <v>117</v>
+      </c>
+      <c r="C60" s="1">
+        <v>46111</v>
       </c>
       <c r="D60" s="1">
         <v>46199</v>
@@ -2782,13 +2749,13 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
-      </c>
-      <c r="C61" t="s">
-        <v>80</v>
+        <v>119</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46111</v>
       </c>
       <c r="D61" s="1">
         <v>46114</v>
@@ -2811,13 +2778,13 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
-      </c>
-      <c r="C62" t="s">
-        <v>126</v>
+        <v>121</v>
+      </c>
+      <c r="C62" s="1">
+        <v>46119</v>
       </c>
       <c r="D62" s="1">
         <v>46125</v>
@@ -2840,13 +2807,13 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" t="s">
-        <v>130</v>
+        <v>123</v>
+      </c>
+      <c r="C63" s="1">
+        <v>46126</v>
       </c>
       <c r="D63" s="1">
         <v>46132</v>
@@ -2869,13 +2836,13 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B64" t="s">
-        <v>133</v>
-      </c>
-      <c r="C64" t="s">
-        <v>134</v>
+        <v>125</v>
+      </c>
+      <c r="C64" s="1">
+        <v>46133</v>
       </c>
       <c r="D64" s="1">
         <v>46164</v>
@@ -2898,13 +2865,13 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" t="s">
-        <v>137</v>
+        <v>127</v>
+      </c>
+      <c r="C65" s="1">
+        <v>46168</v>
       </c>
       <c r="D65" s="1">
         <v>46174</v>
@@ -2930,10 +2897,10 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C66" s="1">
         <v>46188</v>
@@ -2962,10 +2929,10 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>140</v>
-      </c>
-      <c r="C67" t="s">
-        <v>80</v>
+        <v>130</v>
+      </c>
+      <c r="C67" s="1">
+        <v>46111</v>
       </c>
       <c r="D67" s="1">
         <v>46164</v>
@@ -2985,13 +2952,13 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
-      </c>
-      <c r="C68" t="s">
-        <v>80</v>
+        <v>132</v>
+      </c>
+      <c r="C68" s="1">
+        <v>46111</v>
       </c>
       <c r="D68" s="1">
         <v>46122</v>
@@ -3014,13 +2981,13 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
-      </c>
-      <c r="C69" t="s">
-        <v>127</v>
+        <v>134</v>
+      </c>
+      <c r="C69" s="1">
+        <v>46125</v>
       </c>
       <c r="D69" s="1">
         <v>46136</v>
@@ -3043,13 +3010,13 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" t="s">
-        <v>147</v>
+        <v>136</v>
+      </c>
+      <c r="C70" s="1">
+        <v>46139</v>
       </c>
       <c r="D70" s="1">
         <v>46164</v>
@@ -3072,13 +3039,13 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B71" t="s">
-        <v>149</v>
-      </c>
-      <c r="C71" t="s">
-        <v>89</v>
+        <v>138</v>
+      </c>
+      <c r="C71" s="1">
+        <v>46142</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3089,10 +3056,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="D72" s="1">
         <v>46154</v>
@@ -3106,10 +3073,10 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>152</v>
-      </c>
-      <c r="C73" t="s">
-        <v>120</v>
+        <v>141</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46104</v>
       </c>
       <c r="D73" s="1">
         <v>46136</v>
@@ -3129,13 +3096,13 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B74" t="s">
-        <v>154</v>
-      </c>
-      <c r="C74" t="s">
-        <v>120</v>
+        <v>143</v>
+      </c>
+      <c r="C74" s="1">
+        <v>46104</v>
       </c>
       <c r="D74" s="1">
         <v>46129</v>
@@ -3158,13 +3125,13 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B75" t="s">
-        <v>156</v>
-      </c>
-      <c r="C75" t="s">
-        <v>80</v>
+        <v>145</v>
+      </c>
+      <c r="C75" s="1">
+        <v>46111</v>
       </c>
       <c r="D75" s="1">
         <v>46129</v>
@@ -3187,13 +3154,13 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="B76" t="s">
-        <v>158</v>
-      </c>
-      <c r="C76" t="s">
-        <v>131</v>
+        <v>147</v>
+      </c>
+      <c r="C76" s="1">
+        <v>46132</v>
       </c>
       <c r="D76" s="1">
         <v>46136</v>
@@ -3216,7 +3183,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C77" s="1">
         <v>46202</v>
@@ -3242,10 +3209,10 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C78" s="1">
         <v>46202</v>
@@ -3268,10 +3235,10 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B79" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C79" s="1">
         <v>46202</v>
@@ -3300,10 +3267,10 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>164</v>
-      </c>
-      <c r="C80" t="s">
-        <v>74</v>
+        <v>153</v>
+      </c>
+      <c r="C80" s="1">
+        <v>46097</v>
       </c>
       <c r="D80" s="1">
         <v>46289</v>
@@ -3326,10 +3293,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>165</v>
-      </c>
-      <c r="C81" t="s">
-        <v>74</v>
+        <v>154</v>
+      </c>
+      <c r="C81" s="1">
+        <v>46097</v>
       </c>
       <c r="D81" s="1">
         <v>46206</v>
@@ -3352,13 +3319,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B82" t="s">
-        <v>167</v>
-      </c>
-      <c r="C82" t="s">
-        <v>74</v>
+        <v>156</v>
+      </c>
+      <c r="C82" s="1">
+        <v>46097</v>
       </c>
       <c r="D82" s="1">
         <v>46101</v>
@@ -3381,10 +3348,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B83" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C83" s="1">
         <v>46188</v>
@@ -3413,10 +3380,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C84" s="1">
         <v>46195</v>
@@ -3445,7 +3412,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C85" s="1">
         <v>46216</v>
@@ -3471,7 +3438,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C86" s="1">
         <v>46216</v>
@@ -3497,10 +3464,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B87" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C87" s="1">
         <v>46216</v>
@@ -3529,10 +3496,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B88" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C88" s="1">
         <v>46230</v>
@@ -3561,10 +3528,10 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B89" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C89" s="1">
         <v>46237</v>
@@ -3593,10 +3560,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C90" s="1">
         <v>46251</v>
@@ -3625,7 +3592,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C91" s="1">
         <v>46216</v>
@@ -3651,10 +3618,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C92" s="1">
         <v>46216</v>
@@ -3683,10 +3650,10 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C93" s="1">
         <v>46225</v>
@@ -3715,10 +3682,10 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C94" s="1">
         <v>46232</v>
@@ -3747,7 +3714,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C95" s="1">
         <v>46239</v>
@@ -3773,10 +3740,10 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C96" s="1">
         <v>46239</v>
@@ -3805,10 +3772,10 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C97" s="1">
         <v>46246</v>
@@ -3837,10 +3804,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C98" s="1">
         <v>46253</v>
@@ -3869,7 +3836,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C99" s="1">
         <v>46216</v>
@@ -3895,10 +3862,10 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B100" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C100" s="1">
         <v>46216</v>
@@ -3927,7 +3894,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C101" s="1">
         <v>46258</v>
@@ -3953,10 +3920,10 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B102" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C102" s="1">
         <v>46258</v>
@@ -3985,7 +3952,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C103" s="1">
         <v>46237</v>
@@ -4011,10 +3978,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B104" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C104" s="1">
         <v>46237</v>
@@ -4043,7 +4010,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C105" s="1">
         <v>46174</v>
@@ -4069,10 +4036,10 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B106" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C106" s="1">
         <v>46174</v>
@@ -4101,10 +4068,10 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B107" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C107" s="1">
         <v>46174</v>
@@ -4133,7 +4100,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C108" s="1">
         <v>46216</v>
@@ -4159,7 +4126,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C109" s="1">
         <v>46216</v>
@@ -4185,10 +4152,10 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B110" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C110" s="1">
         <v>46216</v>
@@ -4217,10 +4184,10 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B111" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C111" s="1">
         <v>46237</v>
@@ -4249,10 +4216,10 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B112" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="C112" s="1">
         <v>46237</v>
@@ -4281,7 +4248,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C113" s="1">
         <v>46216</v>
@@ -4307,10 +4274,10 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B114" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C114" s="1">
         <v>46216</v>
@@ -4339,10 +4306,10 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B115" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C115" s="1">
         <v>46219</v>
@@ -4371,10 +4338,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B116" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C116" s="1">
         <v>46224</v>
@@ -4403,10 +4370,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B117" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C117" s="1">
         <v>46227</v>
@@ -4435,10 +4402,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B118" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C118" s="1">
         <v>46232</v>
@@ -4467,10 +4434,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B119" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C119" s="1">
         <v>46232</v>
@@ -4499,7 +4466,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C120" s="1">
         <v>46156</v>
@@ -4525,7 +4492,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C121" s="1">
         <v>46156</v>
@@ -4551,10 +4518,10 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B122" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C122" s="1">
         <v>46156</v>
@@ -4568,10 +4535,10 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B123" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C123" s="1">
         <v>46160</v>
@@ -4597,10 +4564,10 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B124" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C124" s="1">
         <v>46168</v>
@@ -4626,10 +4593,10 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B125" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C125" s="1">
         <v>46169</v>
@@ -4658,10 +4625,10 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="B126" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C126" s="1">
         <v>46171</v>
@@ -4690,10 +4657,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B127" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="C127" s="1">
         <v>46176</v>
@@ -4722,10 +4689,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B128" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="C128" s="1">
         <v>46185</v>
@@ -4754,10 +4721,10 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B129" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C129" s="1">
         <v>46199</v>
@@ -4786,7 +4753,7 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C130" s="1">
         <v>46171</v>
@@ -4812,10 +4779,10 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B131" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C131" s="1">
         <v>46171</v>
@@ -4844,10 +4811,10 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B132" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C132" s="1">
         <v>46181</v>
@@ -4876,10 +4843,10 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B133" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C133" s="1">
         <v>46188</v>
@@ -4908,7 +4875,7 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C134" s="1">
         <v>46261</v>
@@ -4934,10 +4901,10 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B135" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C135" s="1">
         <v>46261</v>
@@ -4960,10 +4927,10 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B136" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C136" s="1">
         <v>46261</v>
@@ -4992,10 +4959,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="B137" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C137" s="1">
         <v>46276</v>
@@ -5024,10 +4991,10 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B138" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D138" s="1">
         <v>46289</v>
@@ -5050,7 +5017,7 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C139" s="1">
         <v>46094</v>
@@ -5073,10 +5040,10 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="B140" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C140" s="1">
         <v>46094</v>
@@ -5096,10 +5063,10 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B141" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C141" s="1">
         <v>46101</v>

--- a/data/Ferry/CL32-May.xlsx
+++ b/data/Ferry/CL32-May.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5AD563-D512-4745-B573-605061D93836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2D2817-C0EB-4B9D-9348-413FC4F4B1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="219">
   <si>
     <t>Activity ID</t>
   </si>
@@ -71,15 +71,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>Ferry PS Updated Scope May 26 CL32 Programme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Key Dates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Contract Dates</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CD-1000</t>
   </si>
   <si>
@@ -98,9 +89,6 @@
     <t>Terminal Float</t>
   </si>
   <si>
-    <t xml:space="preserve">    Planned Dates</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-PD-1000</t>
   </si>
   <si>
@@ -125,36 +113,18 @@
     <t>Planned Project Completion</t>
   </si>
   <si>
-    <t xml:space="preserve">  PMI's/EWN's/CE's</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-CHA-1010</t>
   </si>
   <si>
     <t>JMS-MAE-PS-EWN-000005 - Naming Conventions and Protocols</t>
   </si>
   <si>
-    <t xml:space="preserve">    FER-CHA-1000</t>
-  </si>
-  <si>
-    <t>JMS-MAE-PS-EWN-000007</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Manhole 1 Weir wall inclusion</t>
-  </si>
-  <si>
-    <t>23-Apr-26 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-CHA-1020</t>
   </si>
   <si>
     <t>JMS001-PS-RFQ-000001 - Optioneering Assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">  Dependencies</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-DEP-1000</t>
   </si>
   <si>
@@ -227,9 +197,6 @@
     <t>[GET] - Catchment Area EPD (Explosion Protection Document)- Confirmation of Hazardous Substances in existing tank</t>
   </si>
   <si>
-    <t xml:space="preserve">  Mobilisation</t>
-  </si>
-  <si>
     <t xml:space="preserve">    FER-MOB-1000</t>
   </si>
   <si>
@@ -260,21 +227,12 @@
     <t>Murphy Response to TQs</t>
   </si>
   <si>
-    <t xml:space="preserve">  Deliverables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    JMS001-PS-RFQ-000001 - Optioneering Assessment</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CHA-1030</t>
   </si>
   <si>
     <t>Outfall pipework optioneering</t>
   </si>
   <si>
-    <t xml:space="preserve">    3D Modelling</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-3D-1020</t>
   </si>
   <si>
@@ -326,9 +284,6 @@
     <t>BIM Execution Plan</t>
   </si>
   <si>
-    <t xml:space="preserve">    Concept Shaft Design</t>
-  </si>
-  <si>
     <t xml:space="preserve">      FER-CSD-1000</t>
   </si>
   <si>
@@ -386,12 +341,6 @@
     <t>CAT2 check on MGE pile design</t>
   </si>
   <si>
-    <t xml:space="preserve">    Outline Design Scope Freeze (Minimum Requirements)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Civils Design</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-CIV-1000</t>
   </si>
   <si>
@@ -428,9 +377,6 @@
     <t>Shaft penetrations &amp; details drawing</t>
   </si>
   <si>
-    <t xml:space="preserve">      Mechanical Design</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-MEC-1000</t>
   </si>
   <si>
@@ -461,9 +407,6 @@
     <t>[GET] response to JMS-MAE-TQ-000044</t>
   </si>
   <si>
-    <t xml:space="preserve">      Process Design</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-PRO-1010</t>
   </si>
   <si>
@@ -482,9 +425,6 @@
     <t>Control Philosophy</t>
   </si>
   <si>
-    <t xml:space="preserve">      Client Review</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-REV-1000</t>
   </si>
   <si>
@@ -497,12 +437,6 @@
     <t>Client Review of Design Pack</t>
   </si>
   <si>
-    <t xml:space="preserve">    Outline Design Submission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Geotechnical</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-GEO-1000</t>
   </si>
   <si>
@@ -521,9 +455,6 @@
     <t>Client Review of GDR</t>
   </si>
   <si>
-    <t xml:space="preserve">        Detailed Shaft Design</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-CIV-1060</t>
   </si>
   <si>
@@ -548,9 +479,6 @@
     <t>Pipe exit details for rising mains</t>
   </si>
   <si>
-    <t xml:space="preserve">        New Manholes</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-CIV-1100</t>
   </si>
   <si>
@@ -569,9 +497,6 @@
     <t>Pipe entry/exit details</t>
   </si>
   <si>
-    <t xml:space="preserve">        Rising Mains</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-CIV-1130</t>
   </si>
   <si>
@@ -590,27 +515,18 @@
     <t>Civils Pipe Design</t>
   </si>
   <si>
-    <t xml:space="preserve">        Instrumentation &amp; Control</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-CIV-1160</t>
   </si>
   <si>
     <t>Tank kiosk enclosure foundation</t>
   </si>
   <si>
-    <t xml:space="preserve">        Storm Tank Air Vent</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-CIV-1170</t>
   </si>
   <si>
     <t>Assessment of exit details</t>
   </si>
   <si>
-    <t xml:space="preserve">        Ducting/Cable Troughs</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-CIV-1180</t>
   </si>
   <si>
@@ -629,9 +545,6 @@
     <t>HAZOP &amp; ALM action and close out</t>
   </si>
   <si>
-    <t xml:space="preserve">        Documents</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-MEC-1030</t>
   </si>
   <si>
@@ -650,9 +563,6 @@
     <t>Material Take Off</t>
   </si>
   <si>
-    <t xml:space="preserve">        Drawings</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-MEC-1060</t>
   </si>
   <si>
@@ -689,9 +599,6 @@
     <t>Pipework layout plan c/w pipework and manhole schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">      EICA Design</t>
-  </si>
-  <si>
     <t xml:space="preserve">          FER-EICA-1100</t>
   </si>
   <si>
@@ -758,9 +665,6 @@
     <t>DNO/MCC Main Incomer Kiosk Location Plan</t>
   </si>
   <si>
-    <t xml:space="preserve">      Client Review &amp; Design Assurance</t>
-  </si>
-  <si>
     <t xml:space="preserve">        FER-REV-1020</t>
   </si>
   <si>
@@ -777,9 +681,6 @@
   </si>
   <si>
     <t>Final Submission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Retired Activities</t>
   </si>
   <si>
     <t xml:space="preserve">    FER-DEP-1030</t>
@@ -1166,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FEB57D-8EA3-487D-B8BA-A49B4CD8571C}">
-  <dimension ref="A1:K141"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
@@ -1221,40 +1122,40 @@
       <c r="A2" t="s">
         <v>11</v>
       </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" s="1">
         <v>46069</v>
       </c>
-      <c r="D2" s="1">
-        <v>46302</v>
-      </c>
       <c r="E2" s="1">
         <v>46069</v>
       </c>
-      <c r="F2" s="1">
-        <v>46279</v>
-      </c>
       <c r="G2">
-        <v>-17</v>
-      </c>
-      <c r="H2">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>92</v>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3" s="1">
-        <v>46069</v>
+        <v>46290</v>
       </c>
       <c r="D3" s="1">
         <v>46302</v>
       </c>
       <c r="E3" s="1">
-        <v>46069</v>
+        <v>46267</v>
       </c>
       <c r="F3" s="1">
         <v>46279</v>
@@ -1266,22 +1167,24 @@
         <v>-17</v>
       </c>
       <c r="I3">
-        <v>82</v>
+        <v>9</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1">
-        <v>46069</v>
-      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>46302</v>
       </c>
-      <c r="E4" s="1">
-        <v>46069</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1">
         <v>46279</v>
       </c>
@@ -1292,59 +1195,59 @@
         <v>-17</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46069</v>
-      </c>
-      <c r="E5" s="1">
-        <v>46069</v>
+        <v>18</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46185</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46161</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H5">
+        <v>56</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46290</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1">
-        <v>46302</v>
-      </c>
-      <c r="E6" s="1">
-        <v>46267</v>
+        <v>46202</v>
       </c>
       <c r="F6" s="1">
-        <v>46279</v>
+        <v>46177</v>
       </c>
       <c r="G6">
         <v>-17</v>
       </c>
       <c r="H6">
-        <v>-17</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
@@ -1352,18 +1255,16 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1"/>
+        <v>22</v>
+      </c>
       <c r="D7" s="1">
-        <v>46302</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>46289</v>
+      </c>
       <c r="F7" s="1">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="G7">
         <v>-17</v>
@@ -1380,17 +1281,14 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1">
-        <v>46185</v>
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
       </c>
       <c r="D8" s="1">
         <v>46289</v>
       </c>
-      <c r="E8" s="1">
-        <v>46161</v>
-      </c>
       <c r="F8" s="1">
         <v>46266</v>
       </c>
@@ -1401,148 +1299,133 @@
         <v>-17</v>
       </c>
       <c r="I8">
-        <v>73</v>
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46185</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46161</v>
+        <v>26</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46122</v>
+      </c>
+      <c r="E9" s="1">
+        <v>46122</v>
       </c>
       <c r="G9">
-        <v>-17</v>
-      </c>
-      <c r="H9">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46202</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46177</v>
-      </c>
-      <c r="G10">
-        <v>-17</v>
-      </c>
-      <c r="H10">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46153</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46289</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46266</v>
+        <v>30</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46069</v>
+      </c>
+      <c r="E11" s="1">
+        <v>46069</v>
       </c>
       <c r="G11">
-        <v>-17</v>
-      </c>
-      <c r="H11">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46289</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46266</v>
+        <v>32</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46069</v>
+      </c>
+      <c r="E12" s="1">
+        <v>46069</v>
       </c>
       <c r="G12">
-        <v>-17</v>
-      </c>
-      <c r="H12">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
       </c>
       <c r="C13" s="1">
-        <v>46122</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46153</v>
+        <v>46093</v>
       </c>
       <c r="E13" s="1">
-        <v>46122</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46135</v>
+        <v>46093</v>
       </c>
       <c r="G13">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1">
-        <v>46122</v>
+        <v>46094</v>
       </c>
       <c r="E14" s="1">
-        <v>46122</v>
+        <v>46094</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1556,41 +1439,65 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46094</v>
+      </c>
+      <c r="E15" s="1">
+        <v>46094</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="1">
-        <v>46135</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
+        <v>40</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46101</v>
+      </c>
+      <c r="E16" s="1">
+        <v>46101</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1">
-        <v>46153</v>
+        <v>46101</v>
+      </c>
+      <c r="E17" s="1">
+        <v>46101</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1601,42 +1508,39 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
       </c>
       <c r="C18" s="1">
-        <v>46069</v>
-      </c>
-      <c r="D18" s="1">
-        <v>46174</v>
+        <v>46101</v>
       </c>
       <c r="E18" s="1">
-        <v>46069</v>
-      </c>
-      <c r="F18" s="1">
-        <v>46143</v>
+        <v>46101</v>
       </c>
       <c r="G18">
-        <v>-19</v>
-      </c>
-      <c r="H18">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1">
-        <v>46069</v>
+        <v>46101</v>
       </c>
       <c r="E19" s="1">
-        <v>46069</v>
+        <v>46101</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1650,16 +1554,16 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1">
-        <v>46069</v>
+        <v>46101</v>
       </c>
       <c r="E20" s="1">
-        <v>46069</v>
+        <v>46101</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1673,16 +1577,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="E21" s="1">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1696,39 +1600,48 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1">
-        <v>46094</v>
+        <v>46174</v>
       </c>
       <c r="E22" s="1">
-        <v>46094</v>
+        <v>46143</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>-19</v>
+      </c>
+      <c r="H22">
+        <v>36</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1">
-        <v>46094</v>
+        <v>46069</v>
+      </c>
+      <c r="D23" s="1">
+        <v>46073</v>
       </c>
       <c r="E23" s="1">
-        <v>46094</v>
+        <v>46069</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46073</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1742,16 +1655,22 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1">
-        <v>46101</v>
+        <v>46076</v>
+      </c>
+      <c r="D24" s="1">
+        <v>46080</v>
       </c>
       <c r="E24" s="1">
-        <v>46101</v>
+        <v>46076</v>
+      </c>
+      <c r="F24" s="1">
+        <v>46080</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1765,16 +1684,22 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1">
-        <v>46101</v>
+        <v>46090</v>
+      </c>
+      <c r="D25" s="1">
+        <v>46090</v>
       </c>
       <c r="E25" s="1">
-        <v>46101</v>
+        <v>46090</v>
+      </c>
+      <c r="F25" s="1">
+        <v>46090</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1788,16 +1713,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1">
-        <v>46101</v>
+        <v>46090</v>
+      </c>
+      <c r="D26" s="1">
+        <v>46094</v>
       </c>
       <c r="E26" s="1">
-        <v>46101</v>
+        <v>46090</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46094</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1811,16 +1742,22 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1">
-        <v>46101</v>
+        <v>46097</v>
+      </c>
+      <c r="D27" s="1">
+        <v>46108</v>
       </c>
       <c r="E27" s="1">
-        <v>46101</v>
+        <v>46097</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46108</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1834,19 +1771,16 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1">
-        <v>46101</v>
-      </c>
-      <c r="E28" s="1">
-        <v>46101</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
+        <v>46141</v>
+      </c>
+      <c r="D28" s="1">
+        <v>46155</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1857,16 +1791,22 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1">
-        <v>46101</v>
+        <v>46111</v>
+      </c>
+      <c r="D29" s="1">
+        <v>46135</v>
       </c>
       <c r="E29" s="1">
-        <v>46101</v>
+        <v>46111</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46135</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1880,71 +1820,80 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1">
-        <v>46174</v>
+        <v>46111</v>
+      </c>
+      <c r="D30" s="1">
+        <v>46135</v>
       </c>
       <c r="E30" s="1">
-        <v>46143</v>
+        <v>46111</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46135</v>
       </c>
       <c r="G30">
-        <v>-19</v>
-      </c>
-      <c r="H30">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
       </c>
       <c r="C31" s="1">
-        <v>46069</v>
+        <v>46122</v>
       </c>
       <c r="D31" s="1">
-        <v>46108</v>
+        <v>46135</v>
       </c>
       <c r="E31" s="1">
-        <v>46069</v>
+        <v>46122</v>
       </c>
       <c r="F31" s="1">
-        <v>46108</v>
+        <v>46135</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1">
-        <v>46069</v>
+        <v>46136</v>
       </c>
       <c r="D32" s="1">
-        <v>46073</v>
+        <v>46142</v>
       </c>
       <c r="E32" s="1">
-        <v>46069</v>
+        <v>46136</v>
       </c>
       <c r="F32" s="1">
-        <v>46073</v>
+        <v>46142</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1958,172 +1907,205 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C33" s="1">
-        <v>46076</v>
+        <v>46143</v>
       </c>
       <c r="D33" s="1">
-        <v>46080</v>
+        <v>46178</v>
       </c>
       <c r="E33" s="1">
-        <v>46076</v>
+        <v>46143</v>
       </c>
       <c r="F33" s="1">
-        <v>46080</v>
+        <v>46164</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="H33">
+        <v>-17</v>
       </c>
       <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C34" s="1">
-        <v>46090</v>
+        <v>46143</v>
       </c>
       <c r="D34" s="1">
-        <v>46090</v>
+        <v>46178</v>
       </c>
       <c r="E34" s="1">
-        <v>46090</v>
+        <v>46143</v>
       </c>
       <c r="F34" s="1">
-        <v>46090</v>
+        <v>46164</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="H34">
+        <v>-17</v>
       </c>
       <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0.66669999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C35" s="1">
-        <v>46090</v>
-      </c>
-      <c r="D35" s="1">
-        <v>46094</v>
+        <v>46163</v>
       </c>
       <c r="E35" s="1">
-        <v>46090</v>
-      </c>
-      <c r="F35" s="1">
-        <v>46094</v>
+        <v>46143</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35" s="2">
         <v>1</v>
+      </c>
+      <c r="K35" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C36" s="1">
-        <v>46097</v>
+        <v>46174</v>
       </c>
       <c r="D36" s="1">
-        <v>46108</v>
+        <v>46185</v>
       </c>
       <c r="E36" s="1">
-        <v>46097</v>
+        <v>46143</v>
       </c>
       <c r="F36" s="1">
-        <v>46108</v>
+        <v>46157</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>-19</v>
+      </c>
+      <c r="H36">
+        <v>-7</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
       </c>
       <c r="C37" s="1">
-        <v>46097</v>
+        <v>46111</v>
       </c>
       <c r="D37" s="1">
-        <v>46289</v>
+        <v>46114</v>
       </c>
       <c r="E37" s="1">
-        <v>46097</v>
+        <v>46111</v>
       </c>
       <c r="F37" s="1">
-        <v>46266</v>
+        <v>46114</v>
       </c>
       <c r="G37">
-        <v>-17</v>
-      </c>
-      <c r="H37">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>83</v>
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>84</v>
+      </c>
+      <c r="B38" t="s">
+        <v>85</v>
       </c>
       <c r="C38" s="1">
-        <v>46141</v>
+        <v>46111</v>
       </c>
       <c r="D38" s="1">
-        <v>46155</v>
+        <v>46114</v>
+      </c>
+      <c r="E38" s="1">
+        <v>46111</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46114</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C39" s="1">
-        <v>46141</v>
+        <v>46111</v>
       </c>
       <c r="D39" s="1">
-        <v>46155</v>
+        <v>46114</v>
+      </c>
+      <c r="E39" s="1">
+        <v>46111</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46114</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2134,370 +2116,388 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
       </c>
       <c r="C40" s="1">
         <v>46111</v>
       </c>
       <c r="D40" s="1">
-        <v>46185</v>
+        <v>46114</v>
       </c>
       <c r="E40" s="1">
         <v>46111</v>
       </c>
       <c r="F40" s="1">
-        <v>46164</v>
+        <v>46114</v>
       </c>
       <c r="G40">
-        <v>-14</v>
-      </c>
-      <c r="H40">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="J40" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="1">
-        <v>46111</v>
+        <v>91</v>
       </c>
       <c r="D41" s="1">
-        <v>46135</v>
-      </c>
-      <c r="E41" s="1">
-        <v>46111</v>
+        <v>46174</v>
       </c>
       <c r="F41" s="1">
-        <v>46135</v>
+        <v>46147</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H41">
+        <v>-17</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1">
-        <v>46111</v>
+        <v>46174</v>
       </c>
       <c r="D42" s="1">
-        <v>46135</v>
+        <v>46178</v>
       </c>
       <c r="E42" s="1">
-        <v>46111</v>
+        <v>46148</v>
       </c>
       <c r="F42" s="1">
-        <v>46135</v>
+        <v>46154</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H42">
+        <v>-17</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1">
-        <v>46122</v>
+        <v>46181</v>
       </c>
       <c r="D43" s="1">
-        <v>46135</v>
+        <v>46185</v>
       </c>
       <c r="E43" s="1">
-        <v>46122</v>
+        <v>46155</v>
       </c>
       <c r="F43" s="1">
-        <v>46135</v>
+        <v>46161</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H43">
+        <v>-17</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1">
-        <v>46136</v>
+        <v>46188</v>
       </c>
       <c r="D44" s="1">
-        <v>46142</v>
+        <v>46199</v>
       </c>
       <c r="E44" s="1">
-        <v>46136</v>
+        <v>46162</v>
       </c>
       <c r="F44" s="1">
-        <v>46142</v>
+        <v>46176</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H44">
+        <v>-12</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C45" s="1">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D45" s="1">
-        <v>46178</v>
+        <v>46206</v>
       </c>
       <c r="E45" s="1">
-        <v>46143</v>
+        <v>46177</v>
       </c>
       <c r="F45" s="1">
-        <v>46164</v>
+        <v>46183</v>
       </c>
       <c r="G45">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="H45">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="I45">
         <v>5</v>
       </c>
-      <c r="J45" s="3">
-        <v>0.66669999999999996</v>
+      <c r="J45" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1">
-        <v>46143</v>
+        <v>46111</v>
       </c>
       <c r="D46" s="1">
-        <v>46178</v>
+        <v>46114</v>
       </c>
       <c r="E46" s="1">
-        <v>46143</v>
+        <v>46111</v>
       </c>
       <c r="F46" s="1">
-        <v>46164</v>
+        <v>46114</v>
       </c>
       <c r="G46">
-        <v>-9</v>
-      </c>
-      <c r="H46">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>5</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0.66669999999999996</v>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C47" s="1">
-        <v>46163</v>
+        <v>46119</v>
+      </c>
+      <c r="D47" s="1">
+        <v>46125</v>
       </c>
       <c r="E47" s="1">
-        <v>46143</v>
+        <v>46119</v>
+      </c>
+      <c r="F47" s="1">
+        <v>46125</v>
       </c>
       <c r="G47">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
-      </c>
-      <c r="K47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C48" s="1">
+        <v>46126</v>
+      </c>
+      <c r="D48" s="1">
+        <v>46132</v>
+      </c>
+      <c r="E48" s="1">
+        <v>46126</v>
+      </c>
+      <c r="F48" s="1">
+        <v>46132</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46133</v>
+      </c>
+      <c r="D49" s="1">
+        <v>46164</v>
+      </c>
+      <c r="E49" s="1">
+        <v>46133</v>
+      </c>
+      <c r="F49" s="1">
+        <v>46150</v>
+      </c>
+      <c r="G49">
+        <v>-10</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46168</v>
+      </c>
+      <c r="D50" s="1">
         <v>46174</v>
       </c>
-      <c r="D48" s="1">
-        <v>46185</v>
-      </c>
-      <c r="E48" s="1">
-        <v>46143</v>
-      </c>
-      <c r="F48" s="1">
+      <c r="E50" s="1">
+        <v>46153</v>
+      </c>
+      <c r="F50" s="1">
         <v>46157</v>
       </c>
-      <c r="G48">
-        <v>-19</v>
-      </c>
-      <c r="H48">
-        <v>-7</v>
-      </c>
-      <c r="I48">
+      <c r="G50">
+        <v>-10</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D51" s="1">
+        <v>46199</v>
+      </c>
+      <c r="E51" s="1">
+        <v>46162</v>
+      </c>
+      <c r="F51" s="1">
+        <v>46176</v>
+      </c>
+      <c r="G51">
+        <v>-17</v>
+      </c>
+      <c r="H51">
+        <v>-17</v>
+      </c>
+      <c r="I51">
         <v>10</v>
       </c>
-      <c r="J48" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="1">
-        <v>46111</v>
-      </c>
-      <c r="D49" s="1">
-        <v>46206</v>
-      </c>
-      <c r="E49" s="1">
-        <v>46111</v>
-      </c>
-      <c r="F49" s="1">
-        <v>46183</v>
-      </c>
-      <c r="G49">
-        <v>-17</v>
-      </c>
-      <c r="H49">
-        <v>-12</v>
-      </c>
-      <c r="I49">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="1">
-        <v>46111</v>
-      </c>
-      <c r="D50" s="1">
-        <v>46114</v>
-      </c>
-      <c r="E50" s="1">
-        <v>46111</v>
-      </c>
-      <c r="F50" s="1">
-        <v>46114</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="1">
-        <v>46111</v>
-      </c>
-      <c r="D51" s="1">
-        <v>46114</v>
-      </c>
-      <c r="E51" s="1">
-        <v>46111</v>
-      </c>
-      <c r="F51" s="1">
-        <v>46114</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
       <c r="J51" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C52" s="1">
         <v>46111</v>
       </c>
       <c r="D52" s="1">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="E52" s="1">
         <v>46111</v>
       </c>
       <c r="F52" s="1">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2509,410 +2509,386 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1">
+        <v>46125</v>
+      </c>
+      <c r="D53" s="1">
+        <v>46136</v>
+      </c>
+      <c r="E53" s="1">
+        <v>46125</v>
+      </c>
+      <c r="F53" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46139</v>
+      </c>
+      <c r="D54" s="1">
+        <v>46164</v>
+      </c>
+      <c r="E54" s="1">
+        <v>46139</v>
+      </c>
+      <c r="F54" s="1">
+        <v>46153</v>
+      </c>
+      <c r="G54">
+        <v>-9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="1">
+        <v>46142</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="D56" s="1">
+        <v>46154</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="1">
+        <v>46104</v>
+      </c>
+      <c r="D57" s="1">
+        <v>46129</v>
+      </c>
+      <c r="E57" s="1">
+        <v>46104</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46129</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="1">
         <v>46111</v>
       </c>
-      <c r="D53" s="1">
-        <v>46114</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="D58" s="1">
+        <v>46129</v>
+      </c>
+      <c r="E58" s="1">
         <v>46111</v>
       </c>
-      <c r="F53" s="1">
-        <v>46114</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54" t="s">
-        <v>106</v>
-      </c>
-      <c r="D54" s="1">
-        <v>46174</v>
-      </c>
-      <c r="F54" s="1">
-        <v>46147</v>
-      </c>
-      <c r="G54">
-        <v>-17</v>
-      </c>
-      <c r="H54">
-        <v>-17</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2">
-        <v>0</v>
-      </c>
-      <c r="K54" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="1">
-        <v>46174</v>
-      </c>
-      <c r="D55" s="1">
-        <v>46178</v>
-      </c>
-      <c r="E55" s="1">
-        <v>46148</v>
-      </c>
-      <c r="F55" s="1">
-        <v>46154</v>
-      </c>
-      <c r="G55">
-        <v>-17</v>
-      </c>
-      <c r="H55">
-        <v>-17</v>
-      </c>
-      <c r="I55">
+      <c r="F58" s="1">
+        <v>46129</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="1">
+        <v>46132</v>
+      </c>
+      <c r="D59" s="1">
+        <v>46136</v>
+      </c>
+      <c r="E59" s="1">
+        <v>46132</v>
+      </c>
+      <c r="F59" s="1">
+        <v>46136</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" s="1">
+        <v>46202</v>
+      </c>
+      <c r="E60" s="1">
+        <v>46177</v>
+      </c>
+      <c r="G60">
+        <v>-17</v>
+      </c>
+      <c r="H60">
+        <v>-17</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46202</v>
+      </c>
+      <c r="D61" s="1">
+        <v>46213</v>
+      </c>
+      <c r="E61" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F61" s="1">
+        <v>46190</v>
+      </c>
+      <c r="G61">
+        <v>-17</v>
+      </c>
+      <c r="H61">
+        <v>-17</v>
+      </c>
+      <c r="I61">
+        <v>10</v>
+      </c>
+      <c r="J61" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" s="1">
+        <v>46097</v>
+      </c>
+      <c r="D62" s="1">
+        <v>46101</v>
+      </c>
+      <c r="E62" s="1">
+        <v>46097</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46101</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C63" s="1">
+        <v>46188</v>
+      </c>
+      <c r="D63" s="1">
+        <v>46192</v>
+      </c>
+      <c r="E63" s="1">
+        <v>46162</v>
+      </c>
+      <c r="F63" s="1">
+        <v>46169</v>
+      </c>
+      <c r="G63">
+        <v>-17</v>
+      </c>
+      <c r="H63">
+        <v>21</v>
+      </c>
+      <c r="I63">
         <v>5</v>
       </c>
-      <c r="J55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="1">
-        <v>46181</v>
-      </c>
-      <c r="D56" s="1">
-        <v>46185</v>
-      </c>
-      <c r="E56" s="1">
-        <v>46155</v>
-      </c>
-      <c r="F56" s="1">
-        <v>46161</v>
-      </c>
-      <c r="G56">
-        <v>-17</v>
-      </c>
-      <c r="H56">
-        <v>-17</v>
-      </c>
-      <c r="I56">
-        <v>5</v>
-      </c>
-      <c r="J56" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" t="s">
-        <v>113</v>
-      </c>
-      <c r="C57" s="1">
-        <v>46188</v>
-      </c>
-      <c r="D57" s="1">
-        <v>46199</v>
-      </c>
-      <c r="E57" s="1">
-        <v>46162</v>
-      </c>
-      <c r="F57" s="1">
-        <v>46176</v>
-      </c>
-      <c r="G57">
-        <v>-17</v>
-      </c>
-      <c r="H57">
-        <v>-12</v>
-      </c>
-      <c r="I57">
+      <c r="J63" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="1">
+        <v>46195</v>
+      </c>
+      <c r="D64" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E64" s="1">
+        <v>46170</v>
+      </c>
+      <c r="F64" s="1">
+        <v>46183</v>
+      </c>
+      <c r="G64">
+        <v>-17</v>
+      </c>
+      <c r="H64">
+        <v>21</v>
+      </c>
+      <c r="I64">
         <v>10</v>
       </c>
-      <c r="J57" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="1">
-        <v>46202</v>
-      </c>
-      <c r="D58" s="1">
-        <v>46206</v>
-      </c>
-      <c r="E58" s="1">
-        <v>46177</v>
-      </c>
-      <c r="F58" s="1">
-        <v>46183</v>
-      </c>
-      <c r="G58">
-        <v>-17</v>
-      </c>
-      <c r="H58">
-        <v>-12</v>
-      </c>
-      <c r="I58">
-        <v>5</v>
-      </c>
-      <c r="J58" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="1">
-        <v>46104</v>
-      </c>
-      <c r="D59" s="1">
-        <v>46213</v>
-      </c>
-      <c r="E59" s="1">
-        <v>46104</v>
-      </c>
-      <c r="F59" s="1">
-        <v>46190</v>
-      </c>
-      <c r="G59">
-        <v>-17</v>
-      </c>
-      <c r="H59">
-        <v>1</v>
-      </c>
-      <c r="I59">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>117</v>
-      </c>
-      <c r="C60" s="1">
-        <v>46111</v>
-      </c>
-      <c r="D60" s="1">
-        <v>46199</v>
-      </c>
-      <c r="E60" s="1">
-        <v>46111</v>
-      </c>
-      <c r="F60" s="1">
-        <v>46176</v>
-      </c>
-      <c r="G60">
-        <v>-17</v>
-      </c>
-      <c r="H60">
-        <v>-17</v>
-      </c>
-      <c r="I60">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>118</v>
-      </c>
-      <c r="B61" t="s">
-        <v>119</v>
-      </c>
-      <c r="C61" s="1">
-        <v>46111</v>
-      </c>
-      <c r="D61" s="1">
-        <v>46114</v>
-      </c>
-      <c r="E61" s="1">
-        <v>46111</v>
-      </c>
-      <c r="F61" s="1">
-        <v>46114</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>120</v>
-      </c>
-      <c r="B62" t="s">
-        <v>121</v>
-      </c>
-      <c r="C62" s="1">
-        <v>46119</v>
-      </c>
-      <c r="D62" s="1">
-        <v>46125</v>
-      </c>
-      <c r="E62" s="1">
-        <v>46119</v>
-      </c>
-      <c r="F62" s="1">
-        <v>46125</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>122</v>
-      </c>
-      <c r="B63" t="s">
-        <v>123</v>
-      </c>
-      <c r="C63" s="1">
-        <v>46126</v>
-      </c>
-      <c r="D63" s="1">
-        <v>46132</v>
-      </c>
-      <c r="E63" s="1">
-        <v>46126</v>
-      </c>
-      <c r="F63" s="1">
-        <v>46132</v>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>124</v>
-      </c>
-      <c r="B64" t="s">
-        <v>125</v>
-      </c>
-      <c r="C64" s="1">
-        <v>46133</v>
-      </c>
-      <c r="D64" s="1">
-        <v>46164</v>
-      </c>
-      <c r="E64" s="1">
-        <v>46133</v>
-      </c>
-      <c r="F64" s="1">
-        <v>46150</v>
-      </c>
-      <c r="G64">
-        <v>-10</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
       <c r="J64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C65" s="1">
-        <v>46168</v>
+        <v>46216</v>
       </c>
       <c r="D65" s="1">
-        <v>46174</v>
+        <v>46227</v>
       </c>
       <c r="E65" s="1">
-        <v>46153</v>
+        <v>46191</v>
       </c>
       <c r="F65" s="1">
-        <v>46157</v>
+        <v>46204</v>
       </c>
       <c r="G65">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>-17</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J65" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C66" s="1">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="D66" s="1">
-        <v>46199</v>
+        <v>46234</v>
       </c>
       <c r="E66" s="1">
-        <v>46162</v>
+        <v>46205</v>
       </c>
       <c r="F66" s="1">
-        <v>46176</v>
+        <v>46211</v>
       </c>
       <c r="G66">
         <v>-17</v>
@@ -2921,7 +2897,7 @@
         <v>-17</v>
       </c>
       <c r="I66">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J66" s="2">
         <v>0</v>
@@ -2929,302 +2905,380 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>130</v>
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
+        <v>144</v>
       </c>
       <c r="C67" s="1">
-        <v>46111</v>
+        <v>46237</v>
       </c>
       <c r="D67" s="1">
-        <v>46164</v>
+        <v>46248</v>
       </c>
       <c r="E67" s="1">
-        <v>46111</v>
+        <v>46212</v>
       </c>
       <c r="F67" s="1">
-        <v>46153</v>
+        <v>46225</v>
       </c>
       <c r="G67">
-        <v>-9</v>
+        <v>-17</v>
+      </c>
+      <c r="H67">
+        <v>-17</v>
       </c>
       <c r="I67">
+        <v>10</v>
+      </c>
+      <c r="J67" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="C68" s="1">
-        <v>46111</v>
+        <v>46251</v>
       </c>
       <c r="D68" s="1">
-        <v>46122</v>
+        <v>46255</v>
       </c>
       <c r="E68" s="1">
-        <v>46111</v>
+        <v>46226</v>
       </c>
       <c r="F68" s="1">
-        <v>46122</v>
+        <v>46232</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H68">
+        <v>-17</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C69" s="1">
-        <v>46125</v>
+        <v>46216</v>
       </c>
       <c r="D69" s="1">
-        <v>46136</v>
+        <v>46224</v>
       </c>
       <c r="E69" s="1">
-        <v>46125</v>
+        <v>46191</v>
       </c>
       <c r="F69" s="1">
-        <v>46136</v>
+        <v>46199</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H69">
+        <v>-16</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C70" s="1">
-        <v>46139</v>
+        <v>46225</v>
       </c>
       <c r="D70" s="1">
-        <v>46164</v>
+        <v>46231</v>
       </c>
       <c r="E70" s="1">
-        <v>46139</v>
+        <v>46202</v>
       </c>
       <c r="F70" s="1">
-        <v>46153</v>
+        <v>46206</v>
       </c>
       <c r="G70">
-        <v>-9</v>
+        <v>-17</v>
+      </c>
+      <c r="H70">
+        <v>-16</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C71" s="1">
-        <v>46142</v>
+        <v>46232</v>
+      </c>
+      <c r="D71" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E71" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F71" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G71">
+        <v>-17</v>
+      </c>
+      <c r="H71">
+        <v>-16</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B72" t="s">
-        <v>140</v>
+        <v>154</v>
+      </c>
+      <c r="C72" s="1">
+        <v>46239</v>
       </c>
       <c r="D72" s="1">
-        <v>46154</v>
+        <v>46245</v>
+      </c>
+      <c r="E72" s="1">
+        <v>46216</v>
+      </c>
+      <c r="F72" s="1">
+        <v>46220</v>
+      </c>
+      <c r="G72">
+        <v>-17</v>
+      </c>
+      <c r="H72">
+        <v>-16</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>141</v>
+        <v>155</v>
+      </c>
+      <c r="B73" t="s">
+        <v>156</v>
       </c>
       <c r="C73" s="1">
-        <v>46104</v>
+        <v>46246</v>
       </c>
       <c r="D73" s="1">
-        <v>46136</v>
+        <v>46252</v>
       </c>
       <c r="E73" s="1">
-        <v>46104</v>
+        <v>46223</v>
       </c>
       <c r="F73" s="1">
-        <v>46136</v>
+        <v>46227</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H73">
+        <v>-16</v>
       </c>
       <c r="I73">
+        <v>5</v>
+      </c>
+      <c r="J73" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="B74" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C74" s="1">
-        <v>46104</v>
+        <v>46253</v>
       </c>
       <c r="D74" s="1">
-        <v>46129</v>
+        <v>46259</v>
       </c>
       <c r="E74" s="1">
-        <v>46104</v>
+        <v>46230</v>
       </c>
       <c r="F74" s="1">
-        <v>46129</v>
+        <v>46234</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H74">
+        <v>-16</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B75" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C75" s="1">
-        <v>46111</v>
+        <v>46216</v>
       </c>
       <c r="D75" s="1">
-        <v>46129</v>
+        <v>46220</v>
       </c>
       <c r="E75" s="1">
-        <v>46111</v>
+        <v>46191</v>
       </c>
       <c r="F75" s="1">
-        <v>46129</v>
+        <v>46197</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H75">
+        <v>11</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="C76" s="1">
-        <v>46132</v>
+        <v>46258</v>
       </c>
       <c r="D76" s="1">
-        <v>46136</v>
+        <v>46260</v>
       </c>
       <c r="E76" s="1">
-        <v>46132</v>
+        <v>46233</v>
       </c>
       <c r="F76" s="1">
-        <v>46136</v>
+        <v>46237</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H76">
+        <v>-17</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>163</v>
+      </c>
+      <c r="B77" t="s">
+        <v>164</v>
       </c>
       <c r="C77" s="1">
-        <v>46202</v>
+        <v>46237</v>
       </c>
       <c r="D77" s="1">
-        <v>46213</v>
+        <v>46241</v>
       </c>
       <c r="E77" s="1">
-        <v>46177</v>
+        <v>46212</v>
       </c>
       <c r="F77" s="1">
-        <v>46190</v>
+        <v>46218</v>
       </c>
       <c r="G77">
         <v>-17</v>
       </c>
       <c r="H77">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="I77">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="J77" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C78" s="1">
-        <v>46202</v>
+        <v>46174</v>
+      </c>
+      <c r="D78" s="1">
+        <v>46174</v>
       </c>
       <c r="E78" s="1">
-        <v>46177</v>
+        <v>46154</v>
+      </c>
+      <c r="F78" s="1">
+        <v>46154</v>
       </c>
       <c r="G78">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="H78">
-        <v>-17</v>
+        <v>38</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3235,31 +3289,31 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C79" s="1">
-        <v>46202</v>
+        <v>46174</v>
       </c>
       <c r="D79" s="1">
-        <v>46213</v>
+        <v>46183</v>
       </c>
       <c r="E79" s="1">
-        <v>46177</v>
+        <v>46155</v>
       </c>
       <c r="F79" s="1">
-        <v>46190</v>
+        <v>46169</v>
       </c>
       <c r="G79">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H79">
-        <v>-17</v>
+        <v>38</v>
       </c>
       <c r="I79">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J79" s="2">
         <v>0</v>
@@ -3267,112 +3321,127 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>153</v>
+        <v>169</v>
+      </c>
+      <c r="B80" t="s">
+        <v>170</v>
       </c>
       <c r="C80" s="1">
-        <v>46097</v>
+        <v>46216</v>
       </c>
       <c r="D80" s="1">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="E80" s="1">
-        <v>46097</v>
+        <v>46191</v>
       </c>
       <c r="F80" s="1">
-        <v>46266</v>
+        <v>46204</v>
       </c>
       <c r="G80">
         <v>-17</v>
       </c>
       <c r="H80">
-        <v>-17</v>
+        <v>6</v>
       </c>
       <c r="I80">
-        <v>83</v>
+        <v>10</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>154</v>
+        <v>171</v>
+      </c>
+      <c r="B81" t="s">
+        <v>172</v>
       </c>
       <c r="C81" s="1">
-        <v>46097</v>
+        <v>46237</v>
       </c>
       <c r="D81" s="1">
-        <v>46206</v>
+        <v>46241</v>
       </c>
       <c r="E81" s="1">
-        <v>46097</v>
+        <v>46212</v>
       </c>
       <c r="F81" s="1">
-        <v>46183</v>
+        <v>46218</v>
       </c>
       <c r="G81">
         <v>-17</v>
       </c>
       <c r="H81">
-        <v>21</v>
+        <v>-4</v>
       </c>
       <c r="I81">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C82" s="1">
-        <v>46097</v>
+        <v>46237</v>
       </c>
       <c r="D82" s="1">
-        <v>46101</v>
+        <v>46241</v>
       </c>
       <c r="E82" s="1">
-        <v>46097</v>
+        <v>46212</v>
       </c>
       <c r="F82" s="1">
-        <v>46101</v>
+        <v>46218</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="H82">
+        <v>-4</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C83" s="1">
-        <v>46188</v>
+        <v>46216</v>
       </c>
       <c r="D83" s="1">
-        <v>46192</v>
+        <v>46218</v>
       </c>
       <c r="E83" s="1">
-        <v>46162</v>
+        <v>46191</v>
       </c>
       <c r="F83" s="1">
-        <v>46169</v>
+        <v>46195</v>
       </c>
       <c r="G83">
         <v>-17</v>
       </c>
       <c r="H83">
-        <v>21</v>
+        <v>-11</v>
       </c>
       <c r="I83">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J83" s="2">
         <v>0</v>
@@ -3380,31 +3449,31 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C84" s="1">
-        <v>46195</v>
+        <v>46219</v>
       </c>
       <c r="D84" s="1">
-        <v>46206</v>
+        <v>46223</v>
       </c>
       <c r="E84" s="1">
-        <v>46170</v>
+        <v>46196</v>
       </c>
       <c r="F84" s="1">
-        <v>46183</v>
+        <v>46198</v>
       </c>
       <c r="G84">
         <v>-17</v>
       </c>
       <c r="H84">
-        <v>21</v>
+        <v>-11</v>
       </c>
       <c r="I84">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J84" s="2">
         <v>0</v>
@@ -3412,80 +3481,92 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>117</v>
+        <v>179</v>
+      </c>
+      <c r="B85" t="s">
+        <v>180</v>
       </c>
       <c r="C85" s="1">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="D85" s="1">
-        <v>46260</v>
+        <v>46226</v>
       </c>
       <c r="E85" s="1">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="F85" s="1">
-        <v>46237</v>
+        <v>46203</v>
       </c>
       <c r="G85">
         <v>-17</v>
       </c>
       <c r="H85">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="I85">
-        <v>33</v>
+        <v>3</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>161</v>
+        <v>181</v>
+      </c>
+      <c r="B86" t="s">
+        <v>182</v>
       </c>
       <c r="C86" s="1">
-        <v>46216</v>
+        <v>46227</v>
       </c>
       <c r="D86" s="1">
-        <v>46255</v>
+        <v>46231</v>
       </c>
       <c r="E86" s="1">
-        <v>46191</v>
+        <v>46204</v>
       </c>
       <c r="F86" s="1">
-        <v>46232</v>
+        <v>46206</v>
       </c>
       <c r="G86">
         <v>-17</v>
       </c>
       <c r="H86">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="I86">
-        <v>30</v>
+        <v>3</v>
+      </c>
+      <c r="J86" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="B87" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C87" s="1">
-        <v>46216</v>
+        <v>46232</v>
       </c>
       <c r="D87" s="1">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="E87" s="1">
-        <v>46191</v>
+        <v>46209</v>
       </c>
       <c r="F87" s="1">
-        <v>46204</v>
+        <v>46220</v>
       </c>
       <c r="G87">
         <v>-17</v>
       </c>
       <c r="H87">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="I87">
         <v>10</v>
@@ -3496,19 +3577,19 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C88" s="1">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="D88" s="1">
         <v>46234</v>
       </c>
       <c r="E88" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F88" s="1">
         <v>46211</v>
@@ -3517,10 +3598,10 @@
         <v>-17</v>
       </c>
       <c r="H88">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="I88">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J88" s="2">
         <v>0</v>
@@ -3528,185 +3609,170 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B89" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C89" s="1">
-        <v>46237</v>
-      </c>
-      <c r="D89" s="1">
-        <v>46248</v>
-      </c>
-      <c r="E89" s="1">
-        <v>46212</v>
-      </c>
-      <c r="F89" s="1">
-        <v>46225</v>
-      </c>
-      <c r="G89">
-        <v>-17</v>
-      </c>
-      <c r="H89">
-        <v>-17</v>
+        <v>46156</v>
       </c>
       <c r="I89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B90" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C90" s="1">
-        <v>46251</v>
+        <v>46160</v>
       </c>
       <c r="D90" s="1">
-        <v>46255</v>
+        <v>46168</v>
       </c>
       <c r="E90" s="1">
-        <v>46226</v>
+        <v>46139</v>
       </c>
       <c r="F90" s="1">
-        <v>46232</v>
+        <v>46153</v>
       </c>
       <c r="G90">
-        <v>-17</v>
-      </c>
-      <c r="H90">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="I90">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>191</v>
+      </c>
+      <c r="B91" t="s">
+        <v>192</v>
       </c>
       <c r="C91" s="1">
-        <v>46216</v>
+        <v>46168</v>
       </c>
       <c r="D91" s="1">
-        <v>46238</v>
+        <v>46170</v>
       </c>
       <c r="E91" s="1">
-        <v>46191</v>
+        <v>46154</v>
       </c>
       <c r="F91" s="1">
-        <v>46213</v>
+        <v>46156</v>
       </c>
       <c r="G91">
-        <v>-17</v>
-      </c>
-      <c r="H91">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="I91">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="J91" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="B92" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C92" s="1">
-        <v>46216</v>
+        <v>46169</v>
       </c>
       <c r="D92" s="1">
-        <v>46224</v>
+        <v>46175</v>
       </c>
       <c r="E92" s="1">
-        <v>46191</v>
+        <v>46154</v>
       </c>
       <c r="F92" s="1">
-        <v>46199</v>
+        <v>46160</v>
       </c>
       <c r="G92">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H92">
-        <v>-16</v>
+        <v>31</v>
       </c>
       <c r="I92">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B93" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C93" s="1">
-        <v>46225</v>
+        <v>46171</v>
       </c>
       <c r="D93" s="1">
-        <v>46231</v>
+        <v>46184</v>
       </c>
       <c r="E93" s="1">
-        <v>46202</v>
+        <v>46157</v>
       </c>
       <c r="F93" s="1">
-        <v>46206</v>
+        <v>46171</v>
       </c>
       <c r="G93">
-        <v>-17</v>
+        <v>-9</v>
       </c>
       <c r="H93">
-        <v>-16</v>
+        <v>22</v>
       </c>
       <c r="I93">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J93" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C94" s="1">
-        <v>46232</v>
+        <v>46176</v>
       </c>
       <c r="D94" s="1">
-        <v>46238</v>
+        <v>46178</v>
       </c>
       <c r="E94" s="1">
-        <v>46209</v>
+        <v>46161</v>
       </c>
       <c r="F94" s="1">
-        <v>46213</v>
+        <v>46163</v>
       </c>
       <c r="G94">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H94">
-        <v>-16</v>
+        <v>31</v>
       </c>
       <c r="I94">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J94" s="2">
         <v>0</v>
@@ -3714,54 +3780,60 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>177</v>
+        <v>199</v>
+      </c>
+      <c r="B95" t="s">
+        <v>200</v>
       </c>
       <c r="C95" s="1">
-        <v>46239</v>
+        <v>46185</v>
       </c>
       <c r="D95" s="1">
-        <v>46259</v>
+        <v>46198</v>
       </c>
       <c r="E95" s="1">
-        <v>46216</v>
+        <v>46174</v>
       </c>
       <c r="F95" s="1">
-        <v>46234</v>
+        <v>46185</v>
       </c>
       <c r="G95">
-        <v>-17</v>
+        <v>-9</v>
       </c>
       <c r="H95">
-        <v>-16</v>
+        <v>22</v>
       </c>
       <c r="I95">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C96" s="1">
-        <v>46239</v>
+        <v>46199</v>
       </c>
       <c r="D96" s="1">
-        <v>46245</v>
+        <v>46205</v>
       </c>
       <c r="E96" s="1">
-        <v>46216</v>
+        <v>46188</v>
       </c>
       <c r="F96" s="1">
-        <v>46220</v>
+        <v>46192</v>
       </c>
       <c r="G96">
-        <v>-17</v>
+        <v>-9</v>
       </c>
       <c r="H96">
-        <v>-16</v>
+        <v>22</v>
       </c>
       <c r="I96">
         <v>5</v>
@@ -3772,60 +3844,60 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="B97" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C97" s="1">
-        <v>46246</v>
+        <v>46171</v>
       </c>
       <c r="D97" s="1">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="E97" s="1">
-        <v>46223</v>
+        <v>46157</v>
       </c>
       <c r="F97" s="1">
-        <v>46227</v>
+        <v>46163</v>
       </c>
       <c r="G97">
-        <v>-17</v>
+        <v>-9</v>
       </c>
       <c r="H97">
-        <v>-16</v>
+        <v>32</v>
       </c>
       <c r="I97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J97" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="B98" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C98" s="1">
-        <v>46253</v>
+        <v>46181</v>
       </c>
       <c r="D98" s="1">
-        <v>46259</v>
+        <v>46185</v>
       </c>
       <c r="E98" s="1">
-        <v>46230</v>
+        <v>46164</v>
       </c>
       <c r="F98" s="1">
-        <v>46234</v>
+        <v>46171</v>
       </c>
       <c r="G98">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H98">
-        <v>-16</v>
+        <v>31</v>
       </c>
       <c r="I98">
         <v>5</v>
@@ -3836,57 +3908,57 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>184</v>
+        <v>207</v>
+      </c>
+      <c r="B99" t="s">
+        <v>208</v>
       </c>
       <c r="C99" s="1">
-        <v>46216</v>
+        <v>46188</v>
       </c>
       <c r="D99" s="1">
-        <v>46220</v>
+        <v>46192</v>
       </c>
       <c r="E99" s="1">
-        <v>46191</v>
+        <v>46174</v>
       </c>
       <c r="F99" s="1">
-        <v>46197</v>
+        <v>46178</v>
       </c>
       <c r="G99">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="H99">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I99">
         <v>5</v>
       </c>
+      <c r="J99" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="B100" t="s">
-        <v>186</v>
+        <v>130</v>
       </c>
       <c r="C100" s="1">
-        <v>46216</v>
-      </c>
-      <c r="D100" s="1">
-        <v>46220</v>
+        <v>46261</v>
       </c>
       <c r="E100" s="1">
-        <v>46191</v>
-      </c>
-      <c r="F100" s="1">
-        <v>46197</v>
+        <v>46238</v>
       </c>
       <c r="G100">
         <v>-17</v>
       </c>
       <c r="H100">
-        <v>11</v>
+        <v>-17</v>
       </c>
       <c r="I100">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J100" s="2">
         <v>0</v>
@@ -3894,19 +3966,22 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>187</v>
+        <v>210</v>
+      </c>
+      <c r="B101" t="s">
+        <v>132</v>
       </c>
       <c r="C101" s="1">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="D101" s="1">
-        <v>46260</v>
+        <v>46275</v>
       </c>
       <c r="E101" s="1">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="F101" s="1">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="G101">
         <v>-17</v>
@@ -3915,27 +3990,30 @@
         <v>-17</v>
       </c>
       <c r="I101">
-        <v>3</v>
+        <v>10</v>
+      </c>
+      <c r="J101" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="B102" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C102" s="1">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="D102" s="1">
-        <v>46260</v>
+        <v>46289</v>
       </c>
       <c r="E102" s="1">
-        <v>46233</v>
+        <v>46252</v>
       </c>
       <c r="F102" s="1">
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="G102">
         <v>-17</v>
@@ -3944,7 +4022,7 @@
         <v>-17</v>
       </c>
       <c r="I102">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J102" s="2">
         <v>0</v>
@@ -3952,1135 +4030,73 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>190</v>
-      </c>
-      <c r="C103" s="1">
-        <v>46237</v>
+        <v>213</v>
+      </c>
+      <c r="B103" t="s">
+        <v>214</v>
       </c>
       <c r="D103" s="1">
-        <v>46241</v>
-      </c>
-      <c r="E103" s="1">
-        <v>46212</v>
+        <v>46289</v>
       </c>
       <c r="F103" s="1">
-        <v>46218</v>
+        <v>46266</v>
       </c>
       <c r="G103">
         <v>-17</v>
       </c>
       <c r="H103">
-        <v>-4</v>
+        <v>-17</v>
       </c>
       <c r="I103">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="J103" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="B104" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C104" s="1">
-        <v>46237</v>
-      </c>
-      <c r="D104" s="1">
-        <v>46241</v>
+        <v>46094</v>
       </c>
       <c r="E104" s="1">
-        <v>46212</v>
-      </c>
-      <c r="F104" s="1">
-        <v>46218</v>
+        <v>46094</v>
       </c>
       <c r="G104">
-        <v>-17</v>
-      </c>
-      <c r="H104">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I104">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J104" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>141</v>
+        <v>217</v>
+      </c>
+      <c r="B105" t="s">
+        <v>218</v>
       </c>
       <c r="C105" s="1">
-        <v>46174</v>
-      </c>
-      <c r="D105" s="1">
-        <v>46183</v>
+        <v>46101</v>
       </c>
       <c r="E105" s="1">
-        <v>46154</v>
-      </c>
-      <c r="F105" s="1">
-        <v>46169</v>
+        <v>46101</v>
       </c>
       <c r="G105">
-        <v>-10</v>
-      </c>
-      <c r="H105">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I105">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>193</v>
-      </c>
-      <c r="B106" t="s">
-        <v>194</v>
-      </c>
-      <c r="C106" s="1">
-        <v>46174</v>
-      </c>
-      <c r="D106" s="1">
-        <v>46174</v>
-      </c>
-      <c r="E106" s="1">
-        <v>46154</v>
-      </c>
-      <c r="F106" s="1">
-        <v>46154</v>
-      </c>
-      <c r="G106">
-        <v>-12</v>
-      </c>
-      <c r="H106">
-        <v>38</v>
-      </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>195</v>
-      </c>
-      <c r="B107" t="s">
-        <v>196</v>
-      </c>
-      <c r="C107" s="1">
-        <v>46174</v>
-      </c>
-      <c r="D107" s="1">
-        <v>46183</v>
-      </c>
-      <c r="E107" s="1">
-        <v>46155</v>
-      </c>
-      <c r="F107" s="1">
-        <v>46169</v>
-      </c>
-      <c r="G107">
-        <v>-10</v>
-      </c>
-      <c r="H107">
-        <v>38</v>
-      </c>
-      <c r="I107">
-        <v>8</v>
-      </c>
-      <c r="J107" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>130</v>
-      </c>
-      <c r="C108" s="1">
-        <v>46216</v>
-      </c>
-      <c r="D108" s="1">
-        <v>46245</v>
-      </c>
-      <c r="E108" s="1">
-        <v>46191</v>
-      </c>
-      <c r="F108" s="1">
-        <v>46220</v>
-      </c>
-      <c r="G108">
-        <v>-17</v>
-      </c>
-      <c r="H108">
-        <v>-6</v>
-      </c>
-      <c r="I108">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>197</v>
-      </c>
-      <c r="C109" s="1">
-        <v>46216</v>
-      </c>
-      <c r="D109" s="1">
-        <v>46241</v>
-      </c>
-      <c r="E109" s="1">
-        <v>46191</v>
-      </c>
-      <c r="F109" s="1">
-        <v>46218</v>
-      </c>
-      <c r="G109">
-        <v>-17</v>
-      </c>
-      <c r="H109">
-        <v>-4</v>
-      </c>
-      <c r="I109">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>198</v>
-      </c>
-      <c r="B110" t="s">
-        <v>199</v>
-      </c>
-      <c r="C110" s="1">
-        <v>46216</v>
-      </c>
-      <c r="D110" s="1">
-        <v>46227</v>
-      </c>
-      <c r="E110" s="1">
-        <v>46191</v>
-      </c>
-      <c r="F110" s="1">
-        <v>46204</v>
-      </c>
-      <c r="G110">
-        <v>-17</v>
-      </c>
-      <c r="H110">
-        <v>6</v>
-      </c>
-      <c r="I110">
-        <v>10</v>
-      </c>
-      <c r="J110" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>200</v>
-      </c>
-      <c r="B111" t="s">
-        <v>201</v>
-      </c>
-      <c r="C111" s="1">
-        <v>46237</v>
-      </c>
-      <c r="D111" s="1">
-        <v>46241</v>
-      </c>
-      <c r="E111" s="1">
-        <v>46212</v>
-      </c>
-      <c r="F111" s="1">
-        <v>46218</v>
-      </c>
-      <c r="G111">
-        <v>-17</v>
-      </c>
-      <c r="H111">
-        <v>-4</v>
-      </c>
-      <c r="I111">
-        <v>5</v>
-      </c>
-      <c r="J111" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>202</v>
-      </c>
-      <c r="B112" t="s">
-        <v>203</v>
-      </c>
-      <c r="C112" s="1">
-        <v>46237</v>
-      </c>
-      <c r="D112" s="1">
-        <v>46241</v>
-      </c>
-      <c r="E112" s="1">
-        <v>46212</v>
-      </c>
-      <c r="F112" s="1">
-        <v>46218</v>
-      </c>
-      <c r="G112">
-        <v>-17</v>
-      </c>
-      <c r="H112">
-        <v>-4</v>
-      </c>
-      <c r="I112">
-        <v>5</v>
-      </c>
-      <c r="J112" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>204</v>
-      </c>
-      <c r="C113" s="1">
-        <v>46216</v>
-      </c>
-      <c r="D113" s="1">
-        <v>46245</v>
-      </c>
-      <c r="E113" s="1">
-        <v>46191</v>
-      </c>
-      <c r="F113" s="1">
-        <v>46220</v>
-      </c>
-      <c r="G113">
-        <v>-17</v>
-      </c>
-      <c r="H113">
-        <v>-11</v>
-      </c>
-      <c r="I113">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>205</v>
-      </c>
-      <c r="B114" t="s">
-        <v>206</v>
-      </c>
-      <c r="C114" s="1">
-        <v>46216</v>
-      </c>
-      <c r="D114" s="1">
-        <v>46218</v>
-      </c>
-      <c r="E114" s="1">
-        <v>46191</v>
-      </c>
-      <c r="F114" s="1">
-        <v>46195</v>
-      </c>
-      <c r="G114">
-        <v>-17</v>
-      </c>
-      <c r="H114">
-        <v>-11</v>
-      </c>
-      <c r="I114">
-        <v>3</v>
-      </c>
-      <c r="J114" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>207</v>
-      </c>
-      <c r="B115" t="s">
-        <v>208</v>
-      </c>
-      <c r="C115" s="1">
-        <v>46219</v>
-      </c>
-      <c r="D115" s="1">
-        <v>46223</v>
-      </c>
-      <c r="E115" s="1">
-        <v>46196</v>
-      </c>
-      <c r="F115" s="1">
-        <v>46198</v>
-      </c>
-      <c r="G115">
-        <v>-17</v>
-      </c>
-      <c r="H115">
-        <v>-11</v>
-      </c>
-      <c r="I115">
-        <v>3</v>
-      </c>
-      <c r="J115" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>209</v>
-      </c>
-      <c r="B116" t="s">
-        <v>210</v>
-      </c>
-      <c r="C116" s="1">
-        <v>46224</v>
-      </c>
-      <c r="D116" s="1">
-        <v>46226</v>
-      </c>
-      <c r="E116" s="1">
-        <v>46199</v>
-      </c>
-      <c r="F116" s="1">
-        <v>46203</v>
-      </c>
-      <c r="G116">
-        <v>-17</v>
-      </c>
-      <c r="H116">
-        <v>-11</v>
-      </c>
-      <c r="I116">
-        <v>3</v>
-      </c>
-      <c r="J116" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>211</v>
-      </c>
-      <c r="B117" t="s">
-        <v>212</v>
-      </c>
-      <c r="C117" s="1">
-        <v>46227</v>
-      </c>
-      <c r="D117" s="1">
-        <v>46231</v>
-      </c>
-      <c r="E117" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F117" s="1">
-        <v>46206</v>
-      </c>
-      <c r="G117">
-        <v>-17</v>
-      </c>
-      <c r="H117">
-        <v>-11</v>
-      </c>
-      <c r="I117">
-        <v>3</v>
-      </c>
-      <c r="J117" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>213</v>
-      </c>
-      <c r="B118" t="s">
-        <v>214</v>
-      </c>
-      <c r="C118" s="1">
-        <v>46232</v>
-      </c>
-      <c r="D118" s="1">
-        <v>46245</v>
-      </c>
-      <c r="E118" s="1">
-        <v>46209</v>
-      </c>
-      <c r="F118" s="1">
-        <v>46220</v>
-      </c>
-      <c r="G118">
-        <v>-17</v>
-      </c>
-      <c r="H118">
-        <v>-11</v>
-      </c>
-      <c r="I118">
-        <v>10</v>
-      </c>
-      <c r="J118" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>215</v>
-      </c>
-      <c r="B119" t="s">
-        <v>216</v>
-      </c>
-      <c r="C119" s="1">
-        <v>46232</v>
-      </c>
-      <c r="D119" s="1">
-        <v>46234</v>
-      </c>
-      <c r="E119" s="1">
-        <v>46209</v>
-      </c>
-      <c r="F119" s="1">
-        <v>46211</v>
-      </c>
-      <c r="G119">
-        <v>-17</v>
-      </c>
-      <c r="H119">
-        <v>-4</v>
-      </c>
-      <c r="I119">
-        <v>3</v>
-      </c>
-      <c r="J119" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>217</v>
-      </c>
-      <c r="C120" s="1">
-        <v>46156</v>
-      </c>
-      <c r="D120" s="1">
-        <v>46205</v>
-      </c>
-      <c r="E120" s="1">
-        <v>46139</v>
-      </c>
-      <c r="F120" s="1">
-        <v>46192</v>
-      </c>
-      <c r="G120">
-        <v>-9</v>
-      </c>
-      <c r="H120">
-        <v>22</v>
-      </c>
-      <c r="I120">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>197</v>
-      </c>
-      <c r="C121" s="1">
-        <v>46156</v>
-      </c>
-      <c r="D121" s="1">
-        <v>46205</v>
-      </c>
-      <c r="E121" s="1">
-        <v>46139</v>
-      </c>
-      <c r="F121" s="1">
-        <v>46192</v>
-      </c>
-      <c r="G121">
-        <v>-9</v>
-      </c>
-      <c r="H121">
-        <v>22</v>
-      </c>
-      <c r="I121">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>218</v>
-      </c>
-      <c r="B122" t="s">
-        <v>219</v>
-      </c>
-      <c r="C122" s="1">
-        <v>46156</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>220</v>
-      </c>
-      <c r="B123" t="s">
-        <v>221</v>
-      </c>
-      <c r="C123" s="1">
-        <v>46160</v>
-      </c>
-      <c r="D123" s="1">
-        <v>46168</v>
-      </c>
-      <c r="E123" s="1">
-        <v>46139</v>
-      </c>
-      <c r="F123" s="1">
-        <v>46153</v>
-      </c>
-      <c r="G123">
-        <v>-10</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>222</v>
-      </c>
-      <c r="B124" t="s">
-        <v>223</v>
-      </c>
-      <c r="C124" s="1">
-        <v>46168</v>
-      </c>
-      <c r="D124" s="1">
-        <v>46170</v>
-      </c>
-      <c r="E124" s="1">
-        <v>46154</v>
-      </c>
-      <c r="F124" s="1">
-        <v>46156</v>
-      </c>
-      <c r="G124">
-        <v>-9</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>224</v>
-      </c>
-      <c r="B125" t="s">
-        <v>225</v>
-      </c>
-      <c r="C125" s="1">
-        <v>46169</v>
-      </c>
-      <c r="D125" s="1">
-        <v>46175</v>
-      </c>
-      <c r="E125" s="1">
-        <v>46154</v>
-      </c>
-      <c r="F125" s="1">
-        <v>46160</v>
-      </c>
-      <c r="G125">
-        <v>-10</v>
-      </c>
-      <c r="H125">
-        <v>31</v>
-      </c>
-      <c r="I125">
-        <v>2</v>
-      </c>
-      <c r="J125" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>226</v>
-      </c>
-      <c r="B126" t="s">
-        <v>227</v>
-      </c>
-      <c r="C126" s="1">
-        <v>46171</v>
-      </c>
-      <c r="D126" s="1">
-        <v>46184</v>
-      </c>
-      <c r="E126" s="1">
-        <v>46157</v>
-      </c>
-      <c r="F126" s="1">
-        <v>46171</v>
-      </c>
-      <c r="G126">
-        <v>-9</v>
-      </c>
-      <c r="H126">
-        <v>22</v>
-      </c>
-      <c r="I126">
-        <v>9</v>
-      </c>
-      <c r="J126" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>228</v>
-      </c>
-      <c r="B127" t="s">
-        <v>229</v>
-      </c>
-      <c r="C127" s="1">
-        <v>46176</v>
-      </c>
-      <c r="D127" s="1">
-        <v>46178</v>
-      </c>
-      <c r="E127" s="1">
-        <v>46161</v>
-      </c>
-      <c r="F127" s="1">
-        <v>46163</v>
-      </c>
-      <c r="G127">
-        <v>-10</v>
-      </c>
-      <c r="H127">
-        <v>31</v>
-      </c>
-      <c r="I127">
-        <v>3</v>
-      </c>
-      <c r="J127" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>230</v>
-      </c>
-      <c r="B128" t="s">
-        <v>231</v>
-      </c>
-      <c r="C128" s="1">
-        <v>46185</v>
-      </c>
-      <c r="D128" s="1">
-        <v>46198</v>
-      </c>
-      <c r="E128" s="1">
-        <v>46174</v>
-      </c>
-      <c r="F128" s="1">
-        <v>46185</v>
-      </c>
-      <c r="G128">
-        <v>-9</v>
-      </c>
-      <c r="H128">
-        <v>22</v>
-      </c>
-      <c r="I128">
-        <v>10</v>
-      </c>
-      <c r="J128" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>232</v>
-      </c>
-      <c r="B129" t="s">
-        <v>233</v>
-      </c>
-      <c r="C129" s="1">
-        <v>46199</v>
-      </c>
-      <c r="D129" s="1">
-        <v>46205</v>
-      </c>
-      <c r="E129" s="1">
-        <v>46188</v>
-      </c>
-      <c r="F129" s="1">
-        <v>46192</v>
-      </c>
-      <c r="G129">
-        <v>-9</v>
-      </c>
-      <c r="H129">
-        <v>22</v>
-      </c>
-      <c r="I129">
-        <v>5</v>
-      </c>
-      <c r="J129" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>204</v>
-      </c>
-      <c r="C130" s="1">
-        <v>46171</v>
-      </c>
-      <c r="D130" s="1">
-        <v>46192</v>
-      </c>
-      <c r="E130" s="1">
-        <v>46157</v>
-      </c>
-      <c r="F130" s="1">
-        <v>46178</v>
-      </c>
-      <c r="G130">
-        <v>-10</v>
-      </c>
-      <c r="H130">
-        <v>31</v>
-      </c>
-      <c r="I130">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>234</v>
-      </c>
-      <c r="B131" t="s">
-        <v>235</v>
-      </c>
-      <c r="C131" s="1">
-        <v>46171</v>
-      </c>
-      <c r="D131" s="1">
-        <v>46177</v>
-      </c>
-      <c r="E131" s="1">
-        <v>46157</v>
-      </c>
-      <c r="F131" s="1">
-        <v>46163</v>
-      </c>
-      <c r="G131">
-        <v>-9</v>
-      </c>
-      <c r="H131">
-        <v>32</v>
-      </c>
-      <c r="I131">
-        <v>4</v>
-      </c>
-      <c r="J131" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>236</v>
-      </c>
-      <c r="B132" t="s">
-        <v>237</v>
-      </c>
-      <c r="C132" s="1">
-        <v>46181</v>
-      </c>
-      <c r="D132" s="1">
-        <v>46185</v>
-      </c>
-      <c r="E132" s="1">
-        <v>46164</v>
-      </c>
-      <c r="F132" s="1">
-        <v>46171</v>
-      </c>
-      <c r="G132">
-        <v>-10</v>
-      </c>
-      <c r="H132">
-        <v>31</v>
-      </c>
-      <c r="I132">
-        <v>5</v>
-      </c>
-      <c r="J132" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>238</v>
-      </c>
-      <c r="B133" t="s">
-        <v>239</v>
-      </c>
-      <c r="C133" s="1">
-        <v>46188</v>
-      </c>
-      <c r="D133" s="1">
-        <v>46192</v>
-      </c>
-      <c r="E133" s="1">
-        <v>46174</v>
-      </c>
-      <c r="F133" s="1">
-        <v>46178</v>
-      </c>
-      <c r="G133">
-        <v>-10</v>
-      </c>
-      <c r="H133">
-        <v>31</v>
-      </c>
-      <c r="I133">
-        <v>5</v>
-      </c>
-      <c r="J133" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>240</v>
-      </c>
-      <c r="C134" s="1">
-        <v>46261</v>
-      </c>
-      <c r="D134" s="1">
-        <v>46289</v>
-      </c>
-      <c r="E134" s="1">
-        <v>46238</v>
-      </c>
-      <c r="F134" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G134">
-        <v>-17</v>
-      </c>
-      <c r="H134">
-        <v>-17</v>
-      </c>
-      <c r="I134">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>241</v>
-      </c>
-      <c r="B135" t="s">
-        <v>150</v>
-      </c>
-      <c r="C135" s="1">
-        <v>46261</v>
-      </c>
-      <c r="E135" s="1">
-        <v>46238</v>
-      </c>
-      <c r="G135">
-        <v>-17</v>
-      </c>
-      <c r="H135">
-        <v>-17</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>242</v>
-      </c>
-      <c r="B136" t="s">
-        <v>152</v>
-      </c>
-      <c r="C136" s="1">
-        <v>46261</v>
-      </c>
-      <c r="D136" s="1">
-        <v>46275</v>
-      </c>
-      <c r="E136" s="1">
-        <v>46238</v>
-      </c>
-      <c r="F136" s="1">
-        <v>46251</v>
-      </c>
-      <c r="G136">
-        <v>-17</v>
-      </c>
-      <c r="H136">
-        <v>-17</v>
-      </c>
-      <c r="I136">
-        <v>10</v>
-      </c>
-      <c r="J136" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>243</v>
-      </c>
-      <c r="B137" t="s">
-        <v>244</v>
-      </c>
-      <c r="C137" s="1">
-        <v>46276</v>
-      </c>
-      <c r="D137" s="1">
-        <v>46289</v>
-      </c>
-      <c r="E137" s="1">
-        <v>46252</v>
-      </c>
-      <c r="F137" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G137">
-        <v>-17</v>
-      </c>
-      <c r="H137">
-        <v>-17</v>
-      </c>
-      <c r="I137">
-        <v>10</v>
-      </c>
-      <c r="J137" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>245</v>
-      </c>
-      <c r="B138" t="s">
-        <v>246</v>
-      </c>
-      <c r="D138" s="1">
-        <v>46289</v>
-      </c>
-      <c r="F138" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G138">
-        <v>-17</v>
-      </c>
-      <c r="H138">
-        <v>-17</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>247</v>
-      </c>
-      <c r="C139" s="1">
-        <v>46094</v>
-      </c>
-      <c r="D139" s="1">
-        <v>46101</v>
-      </c>
-      <c r="E139" s="1">
-        <v>46094</v>
-      </c>
-      <c r="F139" s="1">
-        <v>46101</v>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>248</v>
-      </c>
-      <c r="B140" t="s">
-        <v>249</v>
-      </c>
-      <c r="C140" s="1">
-        <v>46094</v>
-      </c>
-      <c r="E140" s="1">
-        <v>46094</v>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>250</v>
-      </c>
-      <c r="B141" t="s">
-        <v>251</v>
-      </c>
-      <c r="C141" s="1">
-        <v>46101</v>
-      </c>
-      <c r="E141" s="1">
-        <v>46101</v>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2">
         <v>1</v>
       </c>
     </row>

--- a/data/Ferry/CL32-May.xlsx
+++ b/data/Ferry/CL32-May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Ferry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2D2817-C0EB-4B9D-9348-413FC4F4B1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1BA463-B116-4968-9CF5-9A376C9758A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E19347DB-D799-4254-8840-4A1125816596}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -699,7 +699,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -725,17 +732,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1138,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1325,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1342,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1365,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1388,7 +1397,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1411,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1434,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1457,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1480,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1503,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1526,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1549,7 +1558,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1572,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1595,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1650,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1679,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1708,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1737,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1766,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1786,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1815,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1844,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1873,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1902,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -1933,8 +1942,8 @@
       <c r="I33">
         <v>5</v>
       </c>
-      <c r="J33" s="3">
-        <v>0.66669999999999996</v>
+      <c r="J33" s="2">
+        <v>66.67</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -1965,8 +1974,8 @@
       <c r="I34">
         <v>5</v>
       </c>
-      <c r="J34" s="3">
-        <v>0.66669999999999996</v>
+      <c r="J34" s="2">
+        <v>66.67</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -1989,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K35" t="s">
         <v>79</v>
@@ -2053,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2082,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2111,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2140,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2326,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2355,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2384,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -2413,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2445,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="2">
-        <v>0.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -2506,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -2535,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="J53" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2564,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -2581,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -2598,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -2627,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -2656,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -2685,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -2772,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -3621,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -3650,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="J90" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -3679,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="J91" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -3711,7 +3720,7 @@
         <v>2</v>
       </c>
       <c r="J92" s="2">
-        <v>0.6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -3743,7 +3752,7 @@
         <v>9</v>
       </c>
       <c r="J93" s="2">
-        <v>0.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -3871,7 +3880,7 @@
         <v>4</v>
       </c>
       <c r="J97" s="2">
-        <v>0.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -3902,7 +3911,7 @@
       <c r="I98">
         <v>5</v>
       </c>
-      <c r="J98" s="2">
+      <c r="J98" s="3">
         <v>0</v>
       </c>
     </row>
@@ -3934,7 +3943,7 @@
       <c r="I99">
         <v>5</v>
       </c>
-      <c r="J99" s="2">
+      <c r="J99" s="3">
         <v>0</v>
       </c>
     </row>
@@ -3960,7 +3969,7 @@
       <c r="I100">
         <v>0</v>
       </c>
-      <c r="J100" s="2">
+      <c r="J100" s="3">
         <v>0</v>
       </c>
     </row>
@@ -3992,7 +4001,7 @@
       <c r="I101">
         <v>10</v>
       </c>
-      <c r="J101" s="2">
+      <c r="J101" s="3">
         <v>0</v>
       </c>
     </row>
@@ -4024,7 +4033,7 @@
       <c r="I102">
         <v>10</v>
       </c>
-      <c r="J102" s="2">
+      <c r="J102" s="3">
         <v>0</v>
       </c>
     </row>
@@ -4050,7 +4059,7 @@
       <c r="I103">
         <v>0</v>
       </c>
-      <c r="J103" s="2">
+      <c r="J103" s="3">
         <v>0</v>
       </c>
     </row>
@@ -4074,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -4097,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="2">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
